--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -6682,37 +6682,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>legacy_interface:puller</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PULL-ROLLER</t>
+          <t>AUX-DRIVES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Puller roller20x22</t>
+          <t>Puller,spool,traverse actuation</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>TPU tread / metal hub</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>AUX_ACTUATION_HOLD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6732,24 +6732,24 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2 rollers,one compliant preload. Drive motor/tach and spring stack not yet manufacturing released.</t>
+          <t>Separate low-power controls, no large third shredder motor.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>legacy_interface:spool</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>SPOOL-ENV</t>
+          <t>CHAIN-A</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>200mm x70 spool reference</t>
+          <t>ANSI35 chain94 pitches</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>User spool reference</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SPOOL_INTERFACE_ONLY</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Side-removable, support shaft/bracket/traverse and powered tensioning remain unqualified.</t>
+          <t>Pitch length895.35mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>AUX-DRIVES</t>
+          <t>CHAIN-B</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Puller,spool,traverse actuation</t>
+          <t>ANSI35 chain84 pitches</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AUX_ACTUATION_HOLD</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Separate low-power controls, no large third shredder motor.</t>
+          <t>Pitch length800.10mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CHAIN-A</t>
+          <t>CTRL-MEGA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ANSI35 chain94 pitches</t>
+          <t>Arduino Mega</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>OWNED</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Pitch length895.35mm. Working load and width to confirm.</t>
+          <t>Reference power allocator is NOT deployable heater firmware.</t>
         </is>
       </c>
     </row>
@@ -6915,12 +6915,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CHAIN-B</t>
+          <t>DRV-TLIMIT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ANSI35 chain84 pitches</t>
+          <t>Mechanical torque limiter</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>TORQUE_LIMITER_HOLD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Pitch length800.10mm. Working load and width to confirm.</t>
+          <t>Shared M1 input; calibration before blade operation.</t>
         </is>
       </c>
     </row>
@@ -6972,17 +6972,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>CTRL-MEGA</t>
+          <t>EL-BTS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Arduino Mega</t>
+          <t>Existing BTS7960 modules</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OWNED</t>
+          <t>OWNED_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware.</t>
+          <t>Do not assume advertised43A continuous.</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DRV-TLIMIT</t>
+          <t>EL-DRV</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Mechanical torque limiter</t>
+          <t>Pololu2995 M1 driver option</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TORQUE_LIMITER_HOLD</t>
+          <t>OPTION_NOT_PURCHASED</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>https://www.pololu.com/product/2995</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Shared M1 input; calibration before blade operation.</t>
+          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
         </is>
       </c>
     </row>
@@ -7086,17 +7086,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EL-BTS</t>
+          <t>EL-TC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Existing BTS7960 modules</t>
+          <t>Adafruit3263 MAX31856</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>OWNED_UNQUALIFIED</t>
+          <t>PURCHASE_CANDIDATE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>https://www.adafruit.com/product/3263</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7121,17 +7121,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous.</t>
+          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EL-DRV</t>
+          <t>FASTENERS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pololu2995 M1 driver option</t>
+          <t>Brackets, metal supports,keys,shims,retainers</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OPTION_NOT_PURCHASED</t>
+          <t>HARDWARE_SCHEDULE_HOLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.pololu.com/product/2995</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
+          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EL-TC</t>
+          <t>FEED-CHUTE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Adafruit3263 MAX31856</t>
+          <t>Metal lined transfer chute</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PURCHASE_CANDIDATE</t>
+          <t>TRANSFER_PATH_HOLD</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.adafruit.com/product/3263</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
+          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FASTENERS</t>
+          <t>GUARDS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brackets, metal supports,keys,shims,retainers</t>
+          <t>Steel cutter containment / chain guards / heat shield</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>HARDWARE_SCHEDULE_HOLD</t>
+          <t>SAFETY_GEOMETRY_HOLD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
+          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FEED-CHUTE</t>
+          <t>SAFE-BRAKE</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Metal lined transfer chute</t>
+          <t>Bus overvoltage/braking protection</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>TRANSFER_PATH_HOLD</t>
+          <t>REGEN_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
+          <t>PSU sink ability unknown; no regeneration assumption.</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GUARDS</t>
+          <t>SAFE-CONTACT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Steel cutter containment / chain guards / heat shield</t>
+          <t>24V coil DC rated contactor</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SAFETY_GEOMETRY_HOLD</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
+          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SAFE-BRAKE</t>
+          <t>SAFE-FUSE</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bus overvoltage/braking protection</t>
+          <t>Branch and mains fuses / holders</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>REGEN_DESIGN_HOLD</t>
+          <t>CIRCUIT_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>PSU sink ability unknown; no regeneration assumption.</t>
+          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
         </is>
       </c>
     </row>
@@ -7485,17 +7485,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SAFE-CONTACT</t>
+          <t>SAFE-LOCK</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>24V coil DC rated contactor</t>
+          <t>Coded/positive-opening guard lock</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
+          <t>Lid and service access, standstill unlock, manual reset.</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SAFE-FUSE</t>
+          <t>SAFE-STOP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Branch and mains fuses / holders</t>
+          <t>Existing E-stop</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CIRCUIT_DESIGN_HOLD</t>
+          <t>OWNED_RATING_VERIFY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7577,17 +7577,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
+          <t>Independent hard cut with contactor; contact configuration verify.</t>
         </is>
       </c>
     </row>
@@ -7599,17 +7599,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SAFE-LOCK</t>
+          <t>SAFE-THERM</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Coded/positive-opening guard lock</t>
+          <t>Independent thermal cutoff chain</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7644,24 +7644,24 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Lid and service access, standstill unlock, manual reset.</t>
+          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SAFE-STOP</t>
+          <t>CHUTE_BODY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Existing E-stop</t>
+          <t>welded S1-&gt;S2 transfer chute (pan + 45deg intake lip + sealed walls + fin-bypass channel)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7671,54 +7671,54 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel sheet 3 mm + 45deg lips</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OWNED_RATING_VERIFY</t>
+          <t>GEOMETRY_PASS_SLOPE_DEFECT_DOCUMENTED</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify.</t>
+          <t>BREP collision-audited; trough floor slope ~1 deg (batch accumulation transport) - UNQUOTED</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SAFE-THERM</t>
+          <t>CHUTE_TROUGH_FLOOR_E</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Independent thermal cutoff chain</t>
+          <t>bolted trough ledge section over the S2 mouth</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>GEOMETRY_PASS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7753,12 +7753,1608 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
+          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DRV-CHAIN-A</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>ANSI35 steel roller chain p=9.525</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>PROCUREMENT_HOLD</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>VP1-STAGE1</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DRV-CHAIN-B</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>#35 roller chain cut to 801 mm (84 links; chain B: input shaft 24T -&gt; S2 12T)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>ANSI35 steel roller chain p=9.525</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>PROCUREMENT_HOLD</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>VP1-STAGE1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=801.07). UNQUOTED: not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EL_CONTACTOR</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>safety contactor</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>24 V coil contactor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EL_CURRENT_LIMITER</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>heater sequencer / current-limit relay bank</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>relay bank MPN unselected</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>CONTROL_UNIMPLEMENTED_IN_FIRMWARE</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Staged heater control hardware: firmware logic UNIMPLEMENTED; interlock required so a firmware fault cannot energize two bands - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EL_DIN_RAIL</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>DIN rail 35 mm top-hat x 210</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>steel rail</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>PROCUREMENT_HOLD</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EL_DRIVER_1</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>stepper/BLDC driver (M1 branch)</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>24 V driver MPN unselected</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EL_DRIVER_2</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>stepper/BLDC driver (M2 branch)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>24 V driver MPN unselected</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EL_DRIVER_3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>stepper/BLDC driver (winder/puller accessory)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>24 V driver MPN unselected</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EL_ESTOP_BOX</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>dual-channel E-stop / lid / service interlock relay box</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>relay box MPN unselected</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EL_OVERTEMP_BOX</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>manual-reset independent overtemperature relay box</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>relay box MPN unselected</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EL_WIRE_DUCT</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>slotted wiring duct x 210</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PVC duct</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>PROCUREMENT_HOLD</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>GUARD_CHAIN_A</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>chain A top-run lid plate</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CONTAINMENT_UNRATED</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>GUARD_CHAIN_B</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>chain B outer guard plate set (4 segments; jackshaft crossing gap)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CONTAINMENT_UNRATED</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>GUARD_LID_INTERLOCK_SEAT</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>hopper-lid interlock switch seat</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CONTAINMENT_UNRATED</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>GUARD_S2_RING</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CONTAINMENT_UNRATED</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PULL_FRAME</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>puller side plates + base (adjustable nip carrier)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>steel plate 5 mm + 3 mm</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Nip 2.5..5.5 mm with positive stop - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>PULL_MOTOR_REF</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>puller gearmotor reference (not selected)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>24 V gearmotor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PULL_NIP_STOP</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>nip positive-stop block (2.5 mm minimum)</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PULL_ROLLER_ADJ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>puller adjustable roller dia 20 x 22 + screw carriage</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>steel; M5 screw</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>PULL_ROLLER_FIXED</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>puller drive roller dia 20 x 22</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>steel; knurl or rubber per TPU grip</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_L</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_R</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>WIND_MOTOR_REF</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>spool gearmotor reference (not selected)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>24 V gearmotor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_DRUM</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>spool drum dia 70 x 58</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>steel tube or printed polymer</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_SHAFT</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>spool shaft dia 16 x 95</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>C45 candidate</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_SCREW</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>traverse lead screw dia 8 x 80</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>steel rod</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -4179,12 +4179,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DRV-SH15R</t>
+          <t>DRV-SH40R</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>KHK SH2-15RH reference</t>
+          <t>KHK SH2-40RH reference</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DRV-SH40L</t>
+          <t>DRV-SP12-B12</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KHK SH2-40LH reference</t>
+          <t>ANSI35 12T sprocket bore12</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4251,17 +4251,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S45C hardened</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>COTS_REFERENCE_SECONDARY_BORE_HOLD</t>
+          <t>CHAIN_TOOTH_PROFILE_AND_LOAD_HOLD</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://khkgears.net/pdf/sh.pdf</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Purchased hardened teeth. 25 face + 10 hub. Do not machine teeth from this OD model. 40T bore modified 18 to20. Opposite-hand mating specified; lower-half key is mirrored before axial flip.</t>
+          <t>9.525 pitch. Roller pocket reference only; exact manufacturer tooth form, width and working load must replace this model.</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4293,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DRV-SH40R</t>
+          <t>DRV-SP24-B20</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KHK SH2-40RH reference</t>
+          <t>ANSI35 24T sprocket bore20</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S45C hardened</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>COTS_REFERENCE_SECONDARY_BORE_HOLD</t>
+          <t>CHAIN_TOOTH_PROFILE_AND_LOAD_HOLD</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://khkgears.net/pdf/sh.pdf</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Purchased hardened teeth. 25 face + 10 hub. Do not machine teeth from this OD model. 40T bore modified 18 to20. Opposite-hand mating specified; lower-half key is mirrored before axial flip.</t>
+          <t>9.525 pitch. Roller pocket reference only; exact manufacturer tooth form, width and working load must replace this model.</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DRV-SP12-B12</t>
+          <t>DRV-SP24-B25</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ANSI35 12T sprocket bore12</t>
+          <t>ANSI35 24T sprocket bore25</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DRV-SP24-B12</t>
+          <t>KEY-4-70</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ANSI35 24T sprocket bore12</t>
+          <t>Parallel key4x4x70</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>C45 ground key stock</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CHAIN_TOOTH_PROFILE_AND_LOAD_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>9.525 pitch. Roller pocket reference only; exact manufacturer tooth form, width and working load must replace this model.</t>
+          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
         </is>
       </c>
     </row>
@@ -4464,32 +4464,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DRV-SP24-B20</t>
+          <t>KEY-6-16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ANSI35 24T sprocket bore20</t>
+          <t>Parallel key6x6x16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>C45 ground key stock</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CHAIN_TOOTH_PROFILE_AND_LOAD_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>REQUOTE_AFTER_QUANTITY_CHANGE</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>9.525 pitch. Roller pocket reference only; exact manufacturer tooth form, width and working load must replace this model.</t>
+          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys. VP1 second jackshaft key cut to 14.8 mm before y388 bearing; fit/strength HOLD.</t>
         </is>
       </c>
     </row>
@@ -4521,12 +4521,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DRV-SP24-B25</t>
+          <t>KEY-6-70</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ANSI35 24T sprocket bore25</t>
+          <t>Parallel key6x6x70</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>C45 ground key stock</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CHAIN_TOOTH_PROFILE_AND_LOAD_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4566,34 +4566,34 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>9.525 pitch. Roller pocket reference only; exact manufacturer tooth form, width and working load must replace this model.</t>
+          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>legacy_interface:drive</t>
+          <t>legacy_interface:drive+frame_mount</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KEY-4-16</t>
+          <t>DRV-M1-PL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Parallel key4x4x16</t>
+          <t>TT60 common motor face plate</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>C45 ground key stock</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4618,29 +4618,29 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>REQUOTE_AFTER_QUANTITY_CHANGE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
+          <t>Motor axis datum(35,32.5); 4x5.5 THRU onPCD45. Confirm motor engagement depth.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>legacy_interface:drive</t>
+          <t>legacy_interface:electrical</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KEY-4-70</t>
+          <t>EL-PSU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Parallel key4x4x70</t>
+          <t>Owned 24V 800W PSU</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4650,17 +4650,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>C45 ground key stock</t>
+          <t>Purchased</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_MOUNTING_PATTERN_UNMEASURED</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4670,34 +4670,34 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
+          <t>No guessed mounting holes. 120x240x65 user measurement; model contains true body only.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>legacy_interface:drive</t>
+          <t>legacy_interface:extruder</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KEY-6-16</t>
+          <t>BR-51102</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Parallel key6x6x16</t>
+          <t>51102 bearing boundary</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4707,17 +4707,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>C45 ground key stock</t>
+          <t>Bearing steel</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>DATASHEET_BOUNDARY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>https://www.nsk.com/engineering/51102-apn.html</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4737,24 +4737,24 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
+          <t>Seal, clearance class and exact suffix must be selected. Bearing envelope is not solid steel in mass estimates.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>legacy_interface:drive</t>
+          <t>legacy_interface:extruder</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KEY-6-70</t>
+          <t>BR-6202</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Parallel key6x6x70</t>
+          <t>6202 bearing boundary</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4764,17 +4764,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>C45 ground key stock</t>
+          <t>Bearing steel</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>STANDARD_SIZE_VERIFY_MPN</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4794,44 +4794,44 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Nominal key blank; stock/female-key fit and deburring to drawing review. No printed keys.</t>
+          <t>Seal, clearance class and exact suffix must be selected. Bearing envelope is not solid steel in mass estimates.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>legacy_interface:drive+frame_mount</t>
+          <t>legacy_interface:extruder</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DRV-M1-PL</t>
+          <t>DRV-M2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TT60 common motor face plate</t>
+          <t>M2 TT GMP60 motor reference</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S355 steel</t>
+          <t>Purchased</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>DATASHEET_INTERFACE_REFERENCE</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>https://www.ttmotor.com/uploads/GMP60-609760127.pdf</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4851,24 +4851,24 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Motor axis datum(35,32.5); 4x5.5 THRU onPCD45. Confirm motor engagement depth.</t>
+          <t>4xM5 PCD45, pilot32, shaft12 D10.9; encoder and wire exit not dimensioned in this option.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>legacy_interface:electrical</t>
+          <t>legacy_interface:extruder</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>EL-PSU</t>
+          <t>EX-BARREL</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned 24V 800W PSU</t>
+          <t>Barrel16.3ID x30OD x256</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>SCM440 nitrided RFQ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>OWNED_MOUNTING_PATTERN_UNMEASURED</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4898,17 +4898,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>No guessed mounting holes. 120x240x65 user measurement; model contains true body only.</t>
+          <t>Radial cold clearance0.15. Honing, straightness, hot fit, feed hole and die pressure sealing require supplier approval.</t>
         </is>
       </c>
     </row>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BR-51102</t>
+          <t>EX-CPL</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>51102 bearing boundary</t>
+          <t>12-to15 split coupling32 long</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bearing steel</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DATASHEET_BOUNDARY</t>
+          <t>CLAMP_TORQUE_HOLD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.nsk.com/engineering/51102-apn.html</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Seal, clearance class and exact suffix must be selected. Bearing envelope is not solid steel in mass estimates.</t>
+          <t>D-shaft jaw and clamping proof pending, no axial load transfer intent.</t>
         </is>
       </c>
     </row>
@@ -4977,12 +4977,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BR-6202</t>
+          <t>EX-DIE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>6202 bearing boundary</t>
+          <t>Die36OD x20 with2mm exit</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bearing steel</t>
+          <t>SCM440 or stainless RFQ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>STANDARD_SIZE_VERIFY_MPN</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Seal, clearance class and exact suffix must be selected. Bearing envelope is not solid steel in mass estimates.</t>
+          <t>2mm die exit is a drawdown candidate for1.75 filament, not final calibration. Heater bore6x38; pressure attachment not yet detailed.</t>
         </is>
       </c>
     </row>
@@ -5034,32 +5034,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DRV-M2</t>
+          <t>EX-H100</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>M2 TT GMP60 motor reference</t>
+          <t>24V100W band heater30ID x40</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Purchased custom</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>DATASHEET_INTERFACE_REFERENCE</t>
+          <t>HEATER_QUOTE_AND_DRAWING_HOLD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.ttmotor.com/uploads/GMP60-609760127.pdf</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4xM5 PCD45, pilot32, shaft12 D10.9; encoder and wire exit not dimensioned in this option.</t>
+          <t>3units100W; power density100/(pi*3cm*4cm)=2.65W/cm2. Lead/clamp bulge not invented.</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5091,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EX-BARREL</t>
+          <t>EX-H60</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Barrel16.3ID x30OD x256</t>
+          <t>24V60W cartridge6x20</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SCM440 nitrided RFQ</t>
+          <t>Purchased custom</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>HEATER_QUOTE_AND_DRAWING_HOLD</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Radial cold clearance0.15. Honing, straightness, hot fit, feed hole and die pressure sealing require supplier approval.</t>
+          <t>Rated60W is requirement, not a verified off-the-shelf product.</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5148,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EX-CPL</t>
+          <t>EX-REAR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>12-to15 split coupling32 long</t>
+          <t>Extruder rear/thrust shaft15</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>SCM440</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CLAMP_TORQUE_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>D-shaft jaw and clamping proof pending, no axial load transfer intent.</t>
+          <t>x213..274 inassembly; collar258..264. No thrust transmitted to M2 bearings; shaft-screw connection detail is manufacturing HOLD.</t>
         </is>
       </c>
     </row>
@@ -5205,12 +5205,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EX-DIE</t>
+          <t>EX-SCREW</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Die36OD x20 with2mm exit</t>
+          <t>16mm x256mm compression screw</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SCM440 or stainless RFQ</t>
+          <t>SCM440 QT/nitriding RFQ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2mm die exit is a drawdown candidate for1.75 filament, not final calibration. Heater bore6x38; pressure attachment not yet detailed.</t>
+          <t>Pitch16, flight2, root10 feed /13 meter, L/D16. CAD flight has square flanks; fillets/tip geometry/finish and nitriding supplier confirmation required.</t>
         </is>
       </c>
     </row>
@@ -5262,32 +5262,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EX-H100</t>
+          <t>EX-THRUST</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>24V100W band heater30ID x40</t>
+          <t>Metal thrust carrier39x60x70</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Purchased custom</t>
+          <t>C45</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HEATER_QUOTE_AND_DRAWING_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -5307,24 +5307,24 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>3units100W; power density100/(pi*3cm*4cm)=2.65W/cm2. Lead/clamp bulge not invented.</t>
+          <t>6202 and51102 distinct radial/thrust functions. Split lid, positive stops and end access need assembly DFM; digital solid only. Four M6 underside pilots atX10/26,Y10/50; mating stand positions232/248,255/295.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>legacy_interface:extruder</t>
+          <t>legacy_interface:feed</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EX-H60</t>
+          <t>FEED-BUF</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>24V60W cartridge6x20</t>
+          <t>Buffer190x48 top /50x40 throat /height73</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5334,17 +5334,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Purchased custom</t>
+          <t>PC outer shell plus metal throat</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HEATER_QUOTE_AND_DRAWING_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5364,24 +5364,24 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Rated60W is requirement, not a verified off-the-shelf product.</t>
+          <t>Internal geometric volume calculated; usable75pct separately stated. Top fits between Y251..299, ahead of pin rings. Cold throat offset to barrel feed X289.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>legacy_interface:extruder</t>
+          <t>legacy_interface:feed</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EX-REAR</t>
+          <t>HOP-LID</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Extruder rear/thrust shaft15</t>
+          <t>Interlocked lid180x140</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SCM440</t>
+          <t>PC with metal strike</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5421,24 +5421,24 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>x213..274 inassembly; collar258..264. No thrust transmitted to M2 bearings; shaft-screw connection detail is manufacturing HOLD.</t>
+          <t>Hinge/guard lock hardware not chosen. NO open-lid operation.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>legacy_interface:extruder</t>
+          <t>legacy_interface:feed</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EX-SCREW</t>
+          <t>HOPPER</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>16mm x256mm compression screw</t>
+          <t>35deg batch hopper</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SCM440 QT/nitriding RFQ</t>
+          <t>PC shell + steel lower liner</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5478,24 +5478,24 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Pitch16, flight2, root10 feed /13 meter, L/D16. CAD flight has square flanks; fillets/tip geometry/finish and nitriding supplier confirmation required.</t>
+          <t>Whole hopper exceeds print limit; must split into &lt;=210mm panels before printing. Closed lid and standstill interlock mandatory; angle is not an access safety measure.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>legacy_interface:extruder</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EX-THRUST</t>
+          <t>FR-2020-320</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Metal thrust carrier39x60x70</t>
+          <t>2020 profile cut320</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5505,17 +5505,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5525,54 +5525,54 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>6202 and51102 distinct radial/thrust functions. Split lid, positive stops and end access need assembly DFM; digital solid only. Four M6 underside pilots atX10/26,Y10/50; mating stand positions232/248,255/295.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>legacy_interface:feed</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FEED-BUF</t>
+          <t>FR-2020-360</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Buffer190x48 top /50x40 throat /height73</t>
+          <t>2020 profile cut 360</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PC outer shell plus metal throat</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -5582,54 +5582,54 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Internal geometric volume calculated; usable75pct separately stated. Top fits between Y251..299, ahead of pin rings. Cold throat offset to barrel feed X289.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>legacy_interface:feed</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HOP-LID</t>
+          <t>FR-2020-400</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Interlocked lid180x140</t>
+          <t>2020 profile cut 400</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PC with metal strike</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5639,54 +5639,54 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Hinge/guard lock hardware not chosen. NO open-lid operation.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>legacy_interface:feed</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HOPPER</t>
+          <t>FR-2020-590</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>35deg batch hopper</t>
+          <t>2020 profile cut 590</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>PC shell + steel lower liner</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Whole hopper exceeds print limit; must split into &lt;=210mm panels before printing. Closed lid and standstill interlock mandatory; angle is not an access safety measure.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5718,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FR-2020-320</t>
+          <t>FR-2040-320</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2020 profile cut320</t>
+          <t>2040 profile cut 320</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5775,17 +5775,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FR-2020-360</t>
+          <t>FR-2040-400</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2020 profile cut 360</t>
+          <t>2040 profile cut 400</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FR-2020-400</t>
+          <t>FR-2040-630</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2020 profile cut 400</t>
+          <t>2040 profile cut 630</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5889,32 +5889,32 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FR-2020-590</t>
+          <t>FR-BASE</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2020 profile cut 590</t>
+          <t>Bottom tray 630x400x3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al 5052</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>SHEET_DFM_HOLD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5924,54 +5924,54 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FR-2040-320</t>
+          <t>DRV-DECK</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2040 profile cut 320</t>
+          <t>Steel drive deck240x194x5</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5981,54 +5981,54 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FR-2040-400</t>
+          <t>DRV-M1-FOOT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2040 profile cut 400</t>
+          <t>M1 steel mounting foot70x50x19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6038,54 +6038,54 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FR-2040-630</t>
+          <t>DRV-RISER12</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2040 profile cut 630</t>
+          <t>Input rear bearing riser34x12x10</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6095,34 +6095,34 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FR-BASE</t>
+          <t>DRV-RISER20</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bottom tray 630x400x3</t>
+          <t>Output rear bearing shim70x18x2.5</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al 5052</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SHEET_DFM_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
+          <t>2.50 ground shim, full metal bearing support.</t>
         </is>
       </c>
     </row>
@@ -6174,12 +6174,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DRV-DECK</t>
+          <t>EX-STAND</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Steel drive deck240x194x5</t>
+          <t>Thrust stand / coaxial motor bridge</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>S355 steel</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
+          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
         </is>
       </c>
     </row>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>DRV-M1-FOOT</t>
+          <t>S1-ROOF-F</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>M1 steel mounting foot70x50x19</t>
+          <t>Front roof bracket30x95x25</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>10mm steel welded/folded</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
+          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
         </is>
       </c>
     </row>
@@ -6288,22 +6288,22 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>DRV-RISER12</t>
+          <t>S1-ROOF-R</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Input rear bearing riser34x12x10</t>
+          <t>Rear roof bracket30x48x25</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>10mm steel welded/folded</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
+          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6345,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DRV-RISER20</t>
+          <t>S2-LEG-L</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Output rear bearing shim70x18x2.5</t>
+          <t>S2 L column / metal foot</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2.50 ground shim, full metal bearing support.</t>
+          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
@@ -6402,17 +6402,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EX-STAND</t>
+          <t>S2-LEG-R</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Thrust stand / coaxial motor bridge</t>
+          <t>S2 R column / metal foot</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6447,44 +6447,44 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
+          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S1-ROOF-F</t>
+          <t>AUX-DRIVES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Front roof bracket30x95x25</t>
+          <t>Puller,spool,traverse actuation</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10mm steel welded/folded</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>AUX_ACTUATION_HOLD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6504,44 +6504,44 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
+          <t>Separate low-power controls, no large third shredder motor.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>S1-ROOF-R</t>
+          <t>CHAIN-A</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rear roof bracket30x48x25</t>
+          <t>ANSI35 chain94 pitches</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>10mm steel welded/folded</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -6561,44 +6561,44 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
+          <t>Pitch length895.35mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>S2-LEG-L</t>
+          <t>CHAIN-B</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>S2 L column / metal foot</t>
+          <t>ANSI35 chain84 pitches</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6618,44 +6618,44 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Pitch length800.10mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S2-LEG-R</t>
+          <t>CTRL-MEGA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>S2 R column / metal foot</t>
+          <t>Arduino Mega</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6665,17 +6665,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Reference power allocator is NOT deployable heater firmware.</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AUX-DRIVES</t>
+          <t>DRV-TLIMIT</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Puller,spool,traverse actuation</t>
+          <t>Mechanical torque limiter</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AUX_ACTUATION_HOLD</t>
+          <t>TORQUE_LIMITER_HOLD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Separate low-power controls, no large third shredder motor.</t>
+          <t>Shared M1 input; calibration before blade operation.</t>
         </is>
       </c>
     </row>
@@ -6744,17 +6744,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CHAIN-A</t>
+          <t>EL-BTS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ANSI35 chain94 pitches</t>
+          <t>Existing BTS7960 modules</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>OWNED_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6779,17 +6779,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Pitch length895.35mm. Working load and width to confirm.</t>
+          <t>Do not assume advertised43A continuous.</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CHAIN-B</t>
+          <t>EL-DRV</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ANSI35 chain84 pitches</t>
+          <t>Pololu2995 M1 driver option</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>OPTION_NOT_PURCHASED</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>https://www.pololu.com/product/2995</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Pitch length800.10mm. Working load and width to confirm.</t>
+          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CTRL-MEGA</t>
+          <t>EL-TC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Arduino Mega</t>
+          <t>Adafruit3263 MAX31856</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>OWNED</t>
+          <t>PURCHASE_CANDIDATE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>https://www.adafruit.com/product/3263</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware.</t>
+          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
         </is>
       </c>
     </row>
@@ -6915,12 +6915,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DRV-TLIMIT</t>
+          <t>FASTENERS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Mechanical torque limiter</t>
+          <t>Brackets, metal supports,keys,shims,retainers</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TORQUE_LIMITER_HOLD</t>
+          <t>HARDWARE_SCHEDULE_HOLD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Shared M1 input; calibration before blade operation.</t>
+          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
         </is>
       </c>
     </row>
@@ -6972,17 +6972,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EL-BTS</t>
+          <t>FEED-CHUTE</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Existing BTS7960 modules</t>
+          <t>Metal lined transfer chute</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OWNED_UNQUALIFIED</t>
+          <t>TRANSFER_PATH_HOLD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7007,17 +7007,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous.</t>
+          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EL-DRV</t>
+          <t>GUARDS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pololu2995 M1 driver option</t>
+          <t>Steel cutter containment / chain guards / heat shield</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>OPTION_NOT_PURCHASED</t>
+          <t>SAFETY_GEOMETRY_HOLD</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.pololu.com/product/2995</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
+          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
         </is>
       </c>
     </row>
@@ -7086,17 +7086,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EL-TC</t>
+          <t>SAFE-BRAKE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Adafruit3263 MAX31856</t>
+          <t>Bus overvoltage/braking protection</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PURCHASE_CANDIDATE</t>
+          <t>REGEN_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.adafruit.com/product/3263</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
+          <t>PSU sink ability unknown; no regeneration assumption.</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FASTENERS</t>
+          <t>SAFE-CONTACT</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brackets, metal supports,keys,shims,retainers</t>
+          <t>24V coil DC rated contactor</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>HARDWARE_SCHEDULE_HOLD</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
+          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
         </is>
       </c>
     </row>
@@ -7200,12 +7200,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FEED-CHUTE</t>
+          <t>SAFE-FUSE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Metal lined transfer chute</t>
+          <t>Branch and mains fuses / holders</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7220,12 +7220,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TRANSFER_PATH_HOLD</t>
+          <t>CIRCUIT_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
+          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
         </is>
       </c>
     </row>
@@ -7257,17 +7257,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GUARDS</t>
+          <t>SAFE-LOCK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Steel cutter containment / chain guards / heat shield</t>
+          <t>Coded/positive-opening guard lock</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SAFETY_GEOMETRY_HOLD</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
+          <t>Lid and service access, standstill unlock, manual reset.</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAFE-BRAKE</t>
+          <t>SAFE-STOP</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bus overvoltage/braking protection</t>
+          <t>Existing E-stop</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>REGEN_DESIGN_HOLD</t>
+          <t>OWNED_RATING_VERIFY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7349,17 +7349,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>PSU sink ability unknown; no regeneration assumption.</t>
+          <t>Independent hard cut with contactor; contact configuration verify.</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SAFE-CONTACT</t>
+          <t>SAFE-THERM</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>24V coil DC rated contactor</t>
+          <t>Independent thermal cutoff chain</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7416,24 +7416,24 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
+          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SAFE-FUSE</t>
+          <t>AUG_BEARINGS</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Branch and mains fuses / holders</t>
+          <t>west split pillow plus east journal cradle for the r3 auger shaft</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>CIRCUIT_DESIGN_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7468,54 +7468,54 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
+          <t>Auger shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SAFE-LOCK</t>
+          <t>AUG_SHAFT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Coded/positive-opening guard lock</t>
+          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; 0.032 mm BRep U-shell gap</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel shaft + steel flight</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7525,29 +7525,29 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Lid and service access, standstill unlock, manual reset.</t>
+          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; S1 pan pickup and S2 handoff need connected validation - UNQUOTED</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>SAFE-STOP</t>
+          <t>AUG_WHEEL</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Existing E-stop</t>
+          <t>16T worm wheel (REFERENCE geometry, unrated), face x359..365, sector web, teeth cut by discrete hobbing of the worm; keyed Ø6 auger bore</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7557,54 +7557,54 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OWNED_RATING_VERIFY</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify.</t>
+          <t>Matched 1.8 mm key and keyway transfer torque to AUG_SHAFT; tooth strength and wear unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SAFE-THERM</t>
+          <t>CHUTE_BODY</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Independent thermal cutoff chain</t>
+          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7614,22 +7614,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel sheet 3 mm + formed trough</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
+          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CHUTE_BODY</t>
+          <t>CHUTE_TROUGH_FLOOR_E</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>welded S1-&gt;S2 transfer chute (pan + 45deg intake lip + sealed walls + fin-bypass channel)</t>
+          <t>bolted trough ledge section over the S2 mouth</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm + 45deg lips</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GEOMETRY_PASS_SLOPE_DEFECT_DOCUMENTED</t>
+          <t>GEOMETRY_PASS</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>BREP collision-audited; trough floor slope ~1 deg (batch accumulation transport) - UNQUOTED</t>
+          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CHUTE_TROUGH_FLOOR_E</t>
+          <t>CROSS_FEED_BEARINGS</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>bolted trough ledge section over the S2 mouth</t>
+          <t>paired cross-feed and idler journal support with structural rails</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm</t>
+          <t>steel plate and journal shells</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GEOMETRY_PASS</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
+          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-A</t>
+          <t>CROSS_FEED_GEAR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
+          <t>12T keyed output gear on transverse feed shaft</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>VP1-STAGE1</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
+          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-B</t>
+          <t>CROSS_FEED_IDLER</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 801 mm (84 links; chain B: input shaft 24T -&gt; S2 12T)</t>
+          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7842,22 +7842,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel reference gear and shaft</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>VP1-STAGE1</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=801.07). UNQUOTED: not 0</t>
+          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>EL_CONTACTOR</t>
+          <t>CROSS_FEED_SHAFT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>safety contactor</t>
+          <t>LH helical screw on y-axis x357/z328 with 9 mm pitch and radius 10 mm flight</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7899,22 +7899,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>24 V coil contactor MPN unselected</t>
+          <t>steel shaft and welded flight</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Active +Y transfer to y250.7; frozen south cap y251..255 remains and final material passage unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>EL_CURRENT_LIMITER</t>
+          <t>CROSS_FEED_SHELL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>heater sequencer / current-limit relay bank</t>
+          <t>U cradle and cap-bore inner-radius 5 mm passive outlet bridge</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7956,22 +7956,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>relay bank MPN unselected</t>
+          <t>formed steel sheet</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CONTROL_UNIMPLEMENTED_IN_FIRMWARE</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Staged heater control hardware: firmware logic UNIMPLEMENTED; interlock required so a firmware fault cannot energize two bands - UNQUOTED</t>
+          <t>Shell does not cut frozen S2 cap; material crossing cap bridge unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>EL_DIN_RAIL</t>
+          <t>DRV-CHAIN-A</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DIN rail 35 mm top-hat x 210</t>
+          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>steel rail</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8023,12 +8023,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE1</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EL_DRIVER_1</t>
+          <t>DRV-CHAIN-B</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M1 branch)</t>
+          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8070,22 +8070,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
         </is>
       </c>
     </row>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EL_DRIVER_2</t>
+          <t>EL_CONTACTOR</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M2 branch)</t>
+          <t>safety contactor</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>24 V coil contactor MPN unselected</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EL_DRIVER_3</t>
+          <t>EL_CURRENT_LIMITER</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (winder/puller accessory)</t>
+          <t>heater sequencer / current-limit relay bank</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8184,22 +8184,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>relay bank MPN unselected</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>CONTROL_REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EL_ESTOP_BOX</t>
+          <t>EL_DIN_RAIL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>dual-channel E-stop / lid / service interlock relay box</t>
+          <t>DIN rail 35 mm top-hat x 210</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>steel rail</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EL_OVERTEMP_BOX</t>
+          <t>EL_DRIVER_1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>manual-reset independent overtemperature relay box</t>
+          <t>stepper/BLDC driver (M1 branch)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EL_WIRE_DUCT</t>
+          <t>EL_DRIVER_2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>slotted wiring duct x 210</t>
+          <t>stepper/BLDC driver (M2 branch)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PVC duct</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_A</t>
+          <t>EL_DRIVER_3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>chain A top-run lid plate</t>
+          <t>stepper/BLDC driver (winder/puller accessory)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_B</t>
+          <t>EL_ESTOP_BOX</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>chain B outer guard plate set (4 segments; jackshaft crossing gap)</t>
+          <t>dual-channel E-stop / lid / service interlock relay box</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8469,17 +8469,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>GUARD_LID_INTERLOCK_SEAT</t>
+          <t>EL_OVERTEMP_BOX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>hopper-lid interlock switch seat</t>
+          <t>manual-reset independent overtemperature relay box</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8526,17 +8526,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>GUARD_S2_RING</t>
+          <t>EL_WIRE_DUCT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
+          <t>slotted wiring duct x 210</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>PVC duct</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PULL_FRAME</t>
+          <t>GUARD_CHAIN_A</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>puller side plates + base (adjustable nip carrier)</t>
+          <t>chain A top-run lid plate</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Nip 2.5..5.5 mm with positive stop - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8682,12 +8682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>GUARD_CHAIN_B</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8739,12 +8739,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>GUARD_LID_INTERLOCK_SEAT</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>nip positive-stop block (2.5 mm minimum)</t>
+          <t>hopper-lid interlock switch seat</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>GUARD_S2_RING</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 x 22 + screw carriage</t>
+          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>steel; M5 screw</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PDL_BEARINGS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8868,22 +8868,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Mounted on the support-plate bosses - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>PDL_CHAIN</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8925,22 +8925,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>PDL_FEED_GEAR</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>PDL_SHAFT</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9039,22 +9039,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel rod C45 candidate</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>PDL_SPROCKET</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9096,22 +9096,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>PDL_WORM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9153,22 +9153,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9195,12 +9195,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>PULL_FRAME</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9210,22 +9210,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel plate 5 mm + 3 mm</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9252,12 +9252,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -9309,50 +9309,677 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>PULL_NIP_STOP</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PULL_ROLLER_ADJ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>steel; M5 screw</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>PULL_ROLLER_FIXED</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>puller drive roller dia 20 x 22</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>steel; knurl or rubber per TPU grip</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NIP_RATING_HOLD</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_L</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_R</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>WIND_MOTOR_REF</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>spool gearmotor reference (not selected)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>24 V gearmotor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_BEARINGS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>steel plate 5 mm + bearing seats</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_DRUM</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>spool drum dia 70 x 58</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>steel tube or printed polymer</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_SHAFT</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>spool shaft dia 16 x 95</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>C45 candidate</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H175" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
+      <c r="I175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LH helical screw on y-axis x357/z328 with 9 mm pitch and radius 10 mm flight</t>
+          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch and radius 10 mm flight</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9480,37 +9480,37 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9552,22 +9552,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9609,22 +9609,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9651,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9666,22 +9666,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9708,12 +9708,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9723,22 +9723,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9780,22 +9780,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9837,22 +9837,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9894,22 +9894,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9936,50 +9936,962 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>12T gear on the south east belt idler</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>steel gear</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>S1_SWEEP_GEAR_N</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>12T gear on the north sweep shaft</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>steel gear</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>S1_SWEEP_GEAR_S</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>12T gear on the south sweep shaft</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>steel gear</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>S1_SWEEP_NORTH</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>north transverse screw x226 y236..359 feeding the central lane</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>steel shaft and flight</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Contact pickup unproven; UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>S1_SWEEP_SOUTH</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>south transverse screw x226 y127..228 feeding the central lane</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>steel shaft and flight</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Contact pickup unproven; UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>S1_TRANSFER_BEARINGS</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>two central idler support rings</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>steel bearing seats</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>S1_TRANSFER_BELT</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>central 17 mm tread from x80 to x233.4 inside the two side loops</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>polymer belt</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Screw pickup unproven; UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>S1_TRANSFER_IDLER</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>central east r2.3 idler at x233.4</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>steel drum</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>TRANSFER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_L</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_R</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>spool flange dia 200</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>steel plate 6 mm</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>WIND_MOTOR_REF</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>spool gearmotor reference (not selected)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>24 V gearmotor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_BEARINGS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>steel plate 5 mm + bearing seats</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_DRUM</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>spool drum dia 70 x 58</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>steel tube or printed polymer</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_SHAFT</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>spool shaft dia 16 x 95</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>C45 candidate</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G191" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H191" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
+      <c r="I191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="K191" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>perforated curved screen reference</t>
+          <t>VP1 gravity-aligned perforated curved screen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C2-CAD</t>
+          <t>C2.1-CAD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Actual perforated C2 generated geometry is integrated; hole diameter does not guarantee maximum particle length</t>
+          <t>Current C2.1 generated screen has 78 straight Ø3 exit paths into buffer; particle capture flow ligament strength mounting and particle length limit remain unverified</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; 0.032 mm BRep U-shell gap</t>
+          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; U-shell bore r9.5, nominal BRep gap 1.085 mm</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; S1 pan pickup and S2 handoff need connected validation - UNQUOTED</t>
+          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; tolerance/runout/heat stack assumed not proven</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch and radius 10 mm flight</t>
+          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Active +Y transfer to y250.7; frozen south cap y251..255 remains and final material passage unproven - UNQUOTED</t>
+          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>U cradle and cap-bore inner-radius 5 mm passive outlet bridge</t>
+          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Shell does not cut frozen S2 cap; material crossing cap bridge unproven - UNQUOTED</t>
+          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>north transverse screw x226 y236..359 feeding the central lane</t>
+          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Contact pickup unproven; UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>south transverse screw x226 y127..228 feeding the central lane</t>
+          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Contact pickup unproven; UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10283,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x233.4 inside the two side loops</t>
+          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>central east r2.3 idler at x233.4</t>
+          <t>central east r2.3 idler at x260</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -5428,17 +5428,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>legacy_interface:feed</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>HOPPER</t>
+          <t>FR-2020-320</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>35deg batch hopper</t>
+          <t>2020 profile cut320</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PC shell + steel lower liner</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5468,17 +5468,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Whole hopper exceeds print limit; must split into &lt;=210mm panels before printing. Closed lid and standstill interlock mandatory; angle is not an access safety measure.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
@@ -5490,17 +5490,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FR-2020-320</t>
+          <t>FR-2020-360</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2020 profile cut320</t>
+          <t>2020 profile cut 360</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5547,17 +5547,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FR-2020-360</t>
+          <t>FR-2020-400</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2020 profile cut 360</t>
+          <t>2020 profile cut 400</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FR-2020-400</t>
+          <t>FR-2020-590</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2020 profile cut 400</t>
+          <t>2020 profile cut 590</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FR-2020-590</t>
+          <t>FR-2040-320</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2020 profile cut 590</t>
+          <t>2040 profile cut 320</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FR-2040-320</t>
+          <t>FR-2040-400</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2040 profile cut 320</t>
+          <t>2040 profile cut 400</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FR-2040-400</t>
+          <t>FR-2040-630</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2040 profile cut 400</t>
+          <t>2040 profile cut 630</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5832,32 +5832,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FR-2040-630</t>
+          <t>FR-BASE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2040 profile cut 630</t>
+          <t>Bottom tray 630x400x3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al 5052</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>SHEET_DFM_HOLD</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5867,34 +5867,34 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FR-BASE</t>
+          <t>DRV-DECK</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bottom tray 630x400x3</t>
+          <t>Steel drive deck240x194x5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al 5052</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SHEET_DFM_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
+          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
         </is>
       </c>
     </row>
@@ -5946,12 +5946,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DRV-DECK</t>
+          <t>DRV-M1-FOOT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Steel drive deck240x194x5</t>
+          <t>M1 steel mounting foot70x50x19</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>S355 steel</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
+          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DRV-M1-FOOT</t>
+          <t>DRV-RISER12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>M1 steel mounting foot70x50x19</t>
+          <t>Input rear bearing riser34x12x10</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
+          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DRV-RISER12</t>
+          <t>DRV-RISER20</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Input rear bearing riser34x12x10</t>
+          <t>Output rear bearing shim70x18x2.5</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
+          <t>2.50 ground shim, full metal bearing support.</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DRV-RISER20</t>
+          <t>EX-STAND</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Output rear bearing shim70x18x2.5</t>
+          <t>Thrust stand / coaxial motor bridge</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2.50 ground shim, full metal bearing support.</t>
+          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
         </is>
       </c>
     </row>
@@ -6174,22 +6174,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>EX-STAND</t>
+          <t>S1-ROOF-F</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Thrust stand / coaxial motor bridge</t>
+          <t>Front roof bracket30x95x25</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>10mm steel welded/folded</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
+          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
         </is>
       </c>
     </row>
@@ -6231,12 +6231,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>S1-ROOF-F</t>
+          <t>S1-ROOF-R</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Front roof bracket30x95x25</t>
+          <t>Rear roof bracket30x48x25</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
+          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S1-ROOF-R</t>
+          <t>S2-LEG-L</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rear roof bracket30x48x25</t>
+          <t>S2 L column / metal foot</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>10mm steel welded/folded</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
+          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S2-LEG-L</t>
+          <t>S2-LEG-R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>S2 L column / metal foot</t>
+          <t>S2 R column / metal foot</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6390,44 +6390,44 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>S2-LEG-R</t>
+          <t>AUX-DRIVES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>S2 R column / metal foot</t>
+          <t>Puller,spool,traverse actuation</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>AUX_ACTUATION_HOLD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Separate low-power controls, no large third shredder motor.</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AUX-DRIVES</t>
+          <t>CHAIN-A</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Puller,spool,traverse actuation</t>
+          <t>ANSI35 chain94 pitches</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AUX_ACTUATION_HOLD</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Separate low-power controls, no large third shredder motor.</t>
+          <t>Pitch length895.35mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHAIN-A</t>
+          <t>CHAIN-B</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ANSI35 chain94 pitches</t>
+          <t>ANSI35 chain84 pitches</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pitch length895.35mm. Working load and width to confirm.</t>
+          <t>Pitch length800.10mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CHAIN-B</t>
+          <t>CTRL-MEGA</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ANSI35 chain84 pitches</t>
+          <t>Arduino Mega</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>OWNED</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6608,17 +6608,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Pitch length800.10mm. Working load and width to confirm.</t>
+          <t>Reference power allocator is NOT deployable heater firmware.</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CTRL-MEGA</t>
+          <t>DRV-TLIMIT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Arduino Mega</t>
+          <t>Mechanical torque limiter</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6650,12 +6650,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>OWNED</t>
+          <t>TORQUE_LIMITER_HOLD</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -6665,17 +6665,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware.</t>
+          <t>Shared M1 input; calibration before blade operation.</t>
         </is>
       </c>
     </row>
@@ -6687,17 +6687,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DRV-TLIMIT</t>
+          <t>EL-BTS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mechanical torque limiter</t>
+          <t>Existing BTS7960 modules</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>TORQUE_LIMITER_HOLD</t>
+          <t>OWNED_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6722,17 +6722,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Shared M1 input; calibration before blade operation.</t>
+          <t>Do not assume advertised43A continuous.</t>
         </is>
       </c>
     </row>
@@ -6744,17 +6744,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EL-BTS</t>
+          <t>EL-DRV</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Existing BTS7960 modules</t>
+          <t>Pololu2995 M1 driver option</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OWNED_UNQUALIFIED</t>
+          <t>OPTION_NOT_PURCHASED</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>https://www.pololu.com/product/2995</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6779,17 +6779,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous.</t>
+          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
         </is>
       </c>
     </row>
@@ -6801,17 +6801,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EL-DRV</t>
+          <t>EL-TC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pololu2995 M1 driver option</t>
+          <t>Adafruit3263 MAX31856</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OPTION_NOT_PURCHASED</t>
+          <t>PURCHASE_CANDIDATE</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.pololu.com/product/2995</t>
+          <t>https://www.adafruit.com/product/3263</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
+          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
         </is>
       </c>
     </row>
@@ -6858,17 +6858,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EL-TC</t>
+          <t>FASTENERS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Adafruit3263 MAX31856</t>
+          <t>Brackets, metal supports,keys,shims,retainers</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>PURCHASE_CANDIDATE</t>
+          <t>HARDWARE_SCHEDULE_HOLD</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.adafruit.com/product/3263</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
+          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
         </is>
       </c>
     </row>
@@ -6915,12 +6915,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FASTENERS</t>
+          <t>FEED-CHUTE</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brackets, metal supports,keys,shims,retainers</t>
+          <t>Metal lined transfer chute</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>HARDWARE_SCHEDULE_HOLD</t>
+          <t>TRANSFER_PATH_HOLD</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
+          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FEED-CHUTE</t>
+          <t>GUARDS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Metal lined transfer chute</t>
+          <t>Steel cutter containment / chain guards / heat shield</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TRANSFER_PATH_HOLD</t>
+          <t>SAFETY_GEOMETRY_HOLD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
+          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GUARDS</t>
+          <t>SAFE-BRAKE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Steel cutter containment / chain guards / heat shield</t>
+          <t>Bus overvoltage/braking protection</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SAFETY_GEOMETRY_HOLD</t>
+          <t>REGEN_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
+          <t>PSU sink ability unknown; no regeneration assumption.</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAFE-BRAKE</t>
+          <t>SAFE-CONTACT</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bus overvoltage/braking protection</t>
+          <t>24V coil DC rated contactor</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>REGEN_DESIGN_HOLD</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>PSU sink ability unknown; no regeneration assumption.</t>
+          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SAFE-CONTACT</t>
+          <t>SAFE-FUSE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>24V coil DC rated contactor</t>
+          <t>Branch and mains fuses / holders</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>CIRCUIT_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
+          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAFE-FUSE</t>
+          <t>SAFE-LOCK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Branch and mains fuses / holders</t>
+          <t>Coded/positive-opening guard lock</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CIRCUIT_DESIGN_HOLD</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
+          <t>Lid and service access, standstill unlock, manual reset.</t>
         </is>
       </c>
     </row>
@@ -7257,17 +7257,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAFE-LOCK</t>
+          <t>SAFE-STOP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coded/positive-opening guard lock</t>
+          <t>Existing E-stop</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>OWNED_RATING_VERIFY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Lid and service access, standstill unlock, manual reset.</t>
+          <t>Independent hard cut with contactor; contact configuration verify.</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAFE-STOP</t>
+          <t>SAFE-THERM</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Existing E-stop</t>
+          <t>Independent thermal cutoff chain</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OWNED_RATING_VERIFY</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -7349,34 +7349,34 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify.</t>
+          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>vp1_stage1_3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SAFE-THERM</t>
+          <t>AUG_BEARINGS</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Independent thermal cutoff chain</t>
+          <t>west split pillow plus east journal cradle for the r3 auger shaft</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7386,22 +7386,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
+          <t>Auger shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AUG_BEARINGS</t>
+          <t>AUG_SHAFT</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>west split pillow plus east journal cradle for the r3 auger shaft</t>
+          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; U-shell bore r9.5, nominal BRep gap 1.085 mm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>steel plate 5 mm</t>
+          <t>steel shaft + steel flight</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Auger shaft supported at both ends - UNQUOTED</t>
+          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; tolerance/runout/heat stack assumed not proven</t>
         </is>
       </c>
     </row>
@@ -7485,12 +7485,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AUG_SHAFT</t>
+          <t>AUG_WHEEL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; U-shell bore r9.5, nominal BRep gap 1.085 mm</t>
+          <t>16T worm wheel (REFERENCE geometry, unrated), face x359..365, sector web, teeth cut by discrete hobbing of the worm; keyed Ø6 auger bore</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>steel shaft + steel flight</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; tolerance/runout/heat stack assumed not proven</t>
+          <t>Matched 1.8 mm key and keyway transfer torque to AUG_SHAFT; tooth strength and wear unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>AUG_WHEEL</t>
+          <t>CHUTE_BODY</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>16T worm wheel (REFERENCE geometry, unrated), face x359..365, sector web, teeth cut by discrete hobbing of the worm; keyed Ø6 auger bore</t>
+          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7557,24 +7557,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>steel (reference)</t>
+          <t>steel sheet 3 mm + formed trough</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>REFERENCE_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
           <t>VP1-STAGE5</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>VP1-STAGE5</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t/>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Matched 1.8 mm key and keyway transfer torque to AUG_SHAFT; tooth strength and wear unqualified - UNQUOTED</t>
+          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7599,12 +7599,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CHUTE_BODY</t>
+          <t>CHUTE_TROUGH_FLOOR_E</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
+          <t>bolted trough ledge section over the S2 mouth</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm + formed trough</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>GEOMETRY_PASS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
+          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CHUTE_TROUGH_FLOOR_E</t>
+          <t>CROSS_FEED_BEARINGS</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>bolted trough ledge section over the S2 mouth</t>
+          <t>paired cross-feed and idler journal support with structural rails</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7671,22 +7671,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm</t>
+          <t>steel plate and journal shells</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>GEOMETRY_PASS</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
+          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CROSS_FEED_BEARINGS</t>
+          <t>CROSS_FEED_GEAR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>paired cross-feed and idler journal support with structural rails</t>
+          <t>12T keyed output gear on transverse feed shaft</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>steel plate and journal shells</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
+          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CROSS_FEED_GEAR</t>
+          <t>CROSS_FEED_IDLER</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>12T keyed output gear on transverse feed shaft</t>
+          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>steel reference gear and shaft</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
+          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CROSS_FEED_IDLER</t>
+          <t>CROSS_FEED_SHAFT</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
+          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>steel reference gear and shaft</t>
+          <t>steel shaft and welded flight</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
+          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHAFT</t>
+          <t>CROSS_FEED_SHELL</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
+          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>steel shaft and welded flight</t>
+          <t>formed steel sheet</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
+          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHELL</t>
+          <t>DRV-CHAIN-A</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
+          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7956,22 +7956,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>formed steel sheet</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE1</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-A</t>
+          <t>DRV-CHAIN-B</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
+          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>VP1-STAGE1</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
+          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-B</t>
+          <t>EL_CONTACTOR</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
+          <t>safety contactor</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8070,22 +8070,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>24 V coil contactor MPN unselected</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EL_CONTACTOR</t>
+          <t>EL_CURRENT_LIMITER</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>safety contactor</t>
+          <t>heater sequencer / current-limit relay bank</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8127,22 +8127,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>24 V coil contactor MPN unselected</t>
+          <t>relay bank MPN unselected</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>CONTROL_REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EL_CURRENT_LIMITER</t>
+          <t>EL_DIN_RAIL</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>heater sequencer / current-limit relay bank</t>
+          <t>DIN rail 35 mm top-hat x 210</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8184,22 +8184,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>relay bank MPN unselected</t>
+          <t>steel rail</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CONTROL_REFERENCE_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EL_DIN_RAIL</t>
+          <t>EL_DRIVER_1</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DIN rail 35 mm top-hat x 210</t>
+          <t>stepper/BLDC driver (M1 branch)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>steel rail</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EL_DRIVER_1</t>
+          <t>EL_DRIVER_2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M1 branch)</t>
+          <t>stepper/BLDC driver (M2 branch)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EL_DRIVER_2</t>
+          <t>EL_DRIVER_3</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M2 branch)</t>
+          <t>stepper/BLDC driver (winder/puller accessory)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EL_DRIVER_3</t>
+          <t>EL_ESTOP_BOX</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (winder/puller accessory)</t>
+          <t>dual-channel E-stop / lid / service interlock relay box</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EL_ESTOP_BOX</t>
+          <t>EL_OVERTEMP_BOX</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>dual-channel E-stop / lid / service interlock relay box</t>
+          <t>manual-reset independent overtemperature relay box</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EL_OVERTEMP_BOX</t>
+          <t>EL_WIRE_DUCT</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>manual-reset independent overtemperature relay box</t>
+          <t>slotted wiring duct x 210</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>PVC duct</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EL_WIRE_DUCT</t>
+          <t>GUARD_CHAIN_A</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>slotted wiring duct x 210</t>
+          <t>chain A top-run lid plate</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PVC duct</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_A</t>
+          <t>GUARD_CHAIN_B</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>chain A top-run lid plate</t>
+          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_B</t>
+          <t>GUARD_LID_INTERLOCK_SEAT</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
+          <t>hopper-lid interlock switch seat</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GUARD_LID_INTERLOCK_SEAT</t>
+          <t>GUARD_S2_RING</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>hopper-lid interlock switch seat</t>
+          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8796,37 +8796,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GUARD_S2_RING</t>
+          <t>HOPPER_FASTENER_M3</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
+          <t>M3 x 12 through-bolt with low-profile head for PC panel to captive steel seam boss</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>steel metric fastener</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>FASTENER_ENVELOPE_HOLD</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
+          <t>M3 clearance holes and captive bosses are modeled; bolts/heads not modeled or selected. Head bearing/seal outside taper and torque/preload must be qualified before fabrication; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PDL_BEARINGS</t>
+          <t>HOPPER_PANEL_L</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, left half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8868,22 +8868,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>steel plate 5 mm</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Mounted on the support-plate bosses - UNQUOTED</t>
+          <t>Actual CAD bbox 119.258 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PDL_CHAIN</t>
+          <t>HOPPER_PANEL_R</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, right half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8925,22 +8925,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
+          <t>Actual CAD bbox 117 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PDL_FEED_GEAR</t>
+          <t>HOPPER_SEAM_FRONT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper front seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PDL_SHAFT</t>
+          <t>HOPPER_SEAM_REAR</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper rear seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9039,22 +9039,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>steel rod C45 candidate</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PDL_SPROCKET</t>
+          <t>PDL_BEARINGS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
+          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
+          <t>Mounted on the support-plate bosses - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PDL_WORM</t>
+          <t>PDL_CHAIN</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
+          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>steel (reference)</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>REFERENCE_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
+          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9195,12 +9195,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PULL_FRAME</t>
+          <t>PDL_FEED_GEAR</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
+          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9210,22 +9210,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
+          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9252,12 +9252,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>PDL_SHAFT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9267,22 +9267,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel rod C45 candidate</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>PDL_SPROCKET</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
+          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9324,22 +9324,22 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>PDL_WORM</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
+          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9381,22 +9381,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>steel; M5 screw</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
+          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PULL_FRAME</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel plate 5 mm + 3 mm</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9480,37 +9480,37 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>S1_BELT</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>polymer belt with steel-supported drums</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Friction and tension unrated; UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>S1_BELT_BEARINGS</t>
+          <t>PULL_NIP_STOP</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>four belt shaft support rings in the side rails</t>
+          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9552,22 +9552,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Bearing selection and loads unqualified; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>S1_BELT_CHAIN</t>
+          <t>PULL_ROLLER_ADJ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>#35 chain from S1B 24T to west belt 12T</t>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9609,22 +9609,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>ANSI35 steel chain</t>
+          <t>steel; M5 screw</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Tension and strength unrated; UNQUOTED</t>
+          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9651,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>S1_BELT_DRIVE</t>
+          <t>PULL_ROLLER_FIXED</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
+          <t>puller drive roller dia 20 x 22</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9666,22 +9666,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>steel shaft and drums</t>
+          <t>steel; knurl or rubber per TPU grip</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9708,22 +9708,22 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>S1_BELT_FOLLOWER</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>12T sprocket on the west belt driver</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9765,12 +9765,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S1_BELT_IDLER</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>steel journals and drums</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Two independent journal halves; UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9822,12 +9822,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S1_SWEEP_BEARINGS</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>two separated sweep bearing rings in the pan rails</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_N</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>12T gear on the north east belt idler</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_S</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>12T gear on the south east belt idler</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_N</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>12T gear on the north sweep shaft</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_S</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>12T gear on the south sweep shaft</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>S1_SWEEP_NORTH</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>S1_SWEEP_SOUTH</t>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
+          <t>12T gear on the south east belt idler</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BEARINGS</t>
+          <t>S1_SWEEP_GEAR_N</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>two central idler support rings</t>
+          <t>12T gear on the north sweep shaft</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BELT</t>
+          <t>S1_SWEEP_GEAR_S</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
+          <t>12T gear on the south sweep shaft</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>polymer belt</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Screw pickup unproven; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_IDLER</t>
+          <t>S1_SWEEP_NORTH</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>central east r2.3 idler at x260</t>
+          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>steel drum</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>S1_SWEEP_SOUTH</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10407,22 +10407,22 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>S1_TRANSFER_BEARINGS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>spool flange dia 200</t>
+          <t>two central idler support rings</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10464,22 +10464,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>steel plate 6 mm</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>S1_TRANSFER_BELT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10521,22 +10521,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>polymer belt</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Screw pickup unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>S1_TRANSFER_IDLER</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>central east r2.3 idler at x260</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10578,22 +10578,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>steel drum</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>WIND_FLANGE_L</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_FLANGE_R</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_MOTOR_REF</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>spool gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -10791,12 +10791,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_SPOOL_BEARINGS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>steel plate 5 mm + bearing seats</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10848,50 +10848,278 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t>WIND_SPOOL_DRUM</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>spool drum dia 70 x 58</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>steel tube or printed polymer</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_SHAFT</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>spool shaft dia 16 x 95</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>C45 candidate</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C195" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F195" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
+      <c r="G195" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
+      <c r="I195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="K195" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Buffer190x48 top /50x40 throat /height73</t>
+          <t>Buffer190x48 top /Ø18 octagonal neck15 /height73</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Internal geometric volume calculated; usable75pct separately stated. Top fits between Y251..299, ahead of pin rings. Cold throat offset to barrel feed X289.</t>
+          <t>Lower Ø13 clear octagon and Ø18 outer vertical neck centred on the Ø20 barrel feed bore at x299,y275. 15 mm neck precedes barrel handoff; 1 mm nominal radial room is not a manufacturing tolerance. Upper mouth fits Y251..299. Cold shell-to-barrel support, seal and independent metal throat liner remain manufacturing HOLD.</t>
         </is>
       </c>
     </row>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Buffer190x48 top /Ø18 octagonal neck15 /height73</t>
+          <t>Steel screen receiver with inset shoulder</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PC outer shell plus metal throat</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Lower Ø13 clear octagon and Ø18 outer vertical neck centred on the Ø20 barrel feed bore at x299,y275. 15 mm neck precedes barrel handoff; 1 mm nominal radial room is not a manufacturing tolerance. Upper mouth fits Y251..299. Cold shell-to-barrel support, seal and independent metal throat liner remain manufacturing HOLD.</t>
+          <t>Original 190x48 mouth at z218, outer envelope z145..218; inset at z210 has inner x245..360,y255.5..294.5, covering the nominal S2 screen-bore columns without touching the screen edge at z215.2. Lower Ø13 clear octagonal throat at x299,y275,z145 with Ø18 outer neck z145..160. Weld to separate steel saddle at z145; fasteners, sealing, thermal isolation and fabrication DFM remain HOLD. No material-flow or physical-release claim.</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5376,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HOP-LID</t>
+          <t>FEED-BUF-CLAMP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Interlocked lid180x140</t>
+          <t>Lower cold-barrel saddle half</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PC with metal strike</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5421,24 +5421,24 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Hinge/guard lock hardware not chosen. NO open-lid operation.</t>
+          <t>Lower half of FEED-BUF-SADDLE; four M5 holes pair upper ears. Ø30.2 nominal bore on Ø30 barrel has 0.1 mm cold radial clearance, with 0.4 mm seam available for preload; torque and metal-to-barrel seal remain DFM HOLD.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:feed</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FR-2020-320</t>
+          <t>FEED-BUF-SADDLE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2020 profile cut320</t>
+          <t>Upper cold-barrel saddle and feed sleeve</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5448,17 +5448,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -5468,54 +5468,54 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Sleeve joins FEED-BUF lower steel face at z145 by qualified weld; upper half of Ø36/Ø30.2 x34 cold-barrel split clamp, 0.4 mm open seam and four M5 through-holes. Bolt preload, weld, seal and thermal fit remain DFM HOLD.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>legacy_interface:frame</t>
+          <t>legacy_interface:feed</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FR-2020-360</t>
+          <t>HOP-LID</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2020 profile cut 360</t>
+          <t>Interlocked lid180x140</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>PC with metal strike</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Hinge/guard lock hardware not chosen. NO open-lid operation.</t>
         </is>
       </c>
     </row>
@@ -5547,17 +5547,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FR-2020-400</t>
+          <t>FR-2020-320</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2020 profile cut 400</t>
+          <t>2020 profile cut320</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FR-2020-590</t>
+          <t>FR-2020-360</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2020 profile cut 590</t>
+          <t>2020 profile cut 360</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FR-2040-320</t>
+          <t>FR-2020-400</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2040 profile cut 320</t>
+          <t>2020 profile cut 400</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FR-2040-400</t>
+          <t>FR-2020-590</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2040 profile cut 400</t>
+          <t>2020 profile cut 590</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FR-2040-630</t>
+          <t>FR-2040-320</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2040 profile cut 630</t>
+          <t>2040 profile cut 320</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5832,32 +5832,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>FR-BASE</t>
+          <t>FR-2040-400</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bottom tray 630x400x3</t>
+          <t>2040 profile cut 400</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al 5052</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>SHEET_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5867,54 +5867,54 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DRV-DECK</t>
+          <t>FR-2040-630</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Steel drive deck240x194x5</t>
+          <t>2040 profile cut 630</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>S355 steel</t>
+          <t>Al extrusion - existing</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5924,34 +5924,34 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>legacy_interface:frame_mount</t>
+          <t>legacy_interface:frame</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DRV-M1-FOOT</t>
+          <t>FR-BASE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>M1 steel mounting foot70x50x19</t>
+          <t>Bottom tray 630x400x3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>Al 5052</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CUSTOM_DFM_HOLD</t>
+          <t>SHEET_DFM_HOLD</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
+          <t>Mains and hot zones require separate partitions; shown base is not sealed containment.</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DRV-RISER12</t>
+          <t>DRV-DECK</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Input rear bearing riser34x12x10</t>
+          <t>Steel drive deck240x194x5</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>S355 steel</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
+          <t>Deck atZ20..25, supported by existing crossmembers. Added4 feet must be included in frame stiffness review.</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>DRV-RISER20</t>
+          <t>DRV-M1-FOOT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Output rear bearing shim70x18x2.5</t>
+          <t>M1 steel mounting foot70x50x19</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2.50 ground shim, full metal bearing support.</t>
+          <t>Motor plate corner holes to vertical face. Base bolts to drive deck, not to a printed carrier.</t>
         </is>
       </c>
     </row>
@@ -6117,12 +6117,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EX-STAND</t>
+          <t>DRV-RISER12</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Thrust stand / coaxial motor bridge</t>
+          <t>Input rear bearing riser34x12x10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
+          <t>Bearing bolt pattern must be transferred to deck after slots/profile series confirmed.</t>
         </is>
       </c>
     </row>
@@ -6174,22 +6174,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>S1-ROOF-F</t>
+          <t>DRV-RISER20</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Front roof bracket30x95x25</t>
+          <t>Output rear bearing shim70x18x2.5</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>10mm steel welded/folded</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
+          <t>2.50 ground shim, full metal bearing support.</t>
         </is>
       </c>
     </row>
@@ -6231,22 +6231,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>S1-ROOF-R</t>
+          <t>EX-STAND</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rear roof bracket30x48x25</t>
+          <t>Thrust stand / coaxial motor bridge</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>10mm steel welded/folded</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
+          <t>M2 and thrust carrier share metal stand on deck; no large right-angle gearbox. Top holes4xM6 to carrier. Weld/bolt/pressure proof remains HOLD.</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S2-LEG-L</t>
+          <t>S1-ROOF-F</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>S2 L column / metal foot</t>
+          <t>Front roof bracket30x95x25</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>10mm steel welded/folded</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Face atY135 against retainer. M6 top hole to existing profile centreY50. Metal roof load path; bend/weld qualification pending.</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S2-LEG-R</t>
+          <t>S1-ROOF-R</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>S2 R column / metal foot</t>
+          <t>Rear roof bracket30x48x25</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Steel</t>
+          <t>10mm steel welded/folded</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6390,44 +6390,44 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
+          <t>Face atY352; M6 profile connection atY390. Do not print this bracket.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AUX-DRIVES</t>
+          <t>S2-LEG-L</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Puller,spool,traverse actuation</t>
+          <t>S2 L column / metal foot</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AUX_ACTUATION_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -6447,44 +6447,44 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Separate low-power controls, no large third shredder motor.</t>
+          <t>Foot bottomZ25; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>system_requirement</t>
+          <t>legacy_interface:frame_mount</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CHAIN-A</t>
+          <t>S2-LEG-R</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ANSI35 chain94 pitches</t>
+          <t>S2 R column / metal foot</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Procurement requirement</t>
+          <t>Steel</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>CUSTOM_DFM_HOLD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Pitch length895.35mm. Working load and width to confirm.</t>
+          <t>Foot bottomZ20; topZ210. Centre mounting holeZ203. L sits on5mm deck, R on2020crossmember. Welded joint and anchors DFM hold.</t>
         </is>
       </c>
     </row>
@@ -6516,12 +6516,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CHAIN-B</t>
+          <t>AUX-DRIVES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ANSI35 chain84 pitches</t>
+          <t>Puller,spool,traverse actuation</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CHAIN_RATING_HOLD</t>
+          <t>AUX_ACTUATION_HOLD</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Pitch length800.10mm. Working load and width to confirm.</t>
+          <t>Separate low-power controls, no large third shredder motor.</t>
         </is>
       </c>
     </row>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CTRL-MEGA</t>
+          <t>CHAIN-A</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Arduino Mega</t>
+          <t>ANSI35 chain94 pitches</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OWNED</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -6608,17 +6608,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware.</t>
+          <t>Pitch length895.35mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>DRV-TLIMIT</t>
+          <t>CHAIN-B</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Mechanical torque limiter</t>
+          <t>ANSI35 chain84 pitches</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TORQUE_LIMITER_HOLD</t>
+          <t>CHAIN_RATING_HOLD</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>Shared M1 input; calibration before blade operation.</t>
+          <t>Pitch length800.10mm. Working load and width to confirm.</t>
         </is>
       </c>
     </row>
@@ -6687,17 +6687,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EL-BTS</t>
+          <t>CTRL-MEGA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Existing BTS7960 modules</t>
+          <t>Arduino Mega</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OWNED_UNQUALIFIED</t>
+          <t>OWNED</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous.</t>
+          <t>Reference power allocator is NOT deployable heater firmware.</t>
         </is>
       </c>
     </row>
@@ -6744,12 +6744,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EL-DRV</t>
+          <t>DRV-TLIMIT</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pololu2995 M1 driver option</t>
+          <t>Mechanical torque limiter</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OPTION_NOT_PURCHASED</t>
+          <t>TORQUE_LIMITER_HOLD</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.pololu.com/product/2995</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
+          <t>Shared M1 input; calibration before blade operation.</t>
         </is>
       </c>
     </row>
@@ -6801,17 +6801,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EL-TC</t>
+          <t>EL-BTS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Adafruit3263 MAX31856</t>
+          <t>Existing BTS7960 modules</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>PURCHASE_CANDIDATE</t>
+          <t>OWNED_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.adafruit.com/product/3263</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6836,17 +6836,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
+          <t>Do not assume advertised43A continuous.</t>
         </is>
       </c>
     </row>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FASTENERS</t>
+          <t>EL-DRV</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brackets, metal supports,keys,shims,retainers</t>
+          <t>Pololu2995 M1 driver option</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6878,12 +6878,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>HARDWARE_SCHEDULE_HOLD</t>
+          <t>OPTION_NOT_PURCHASED</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>https://www.pololu.com/product/2995</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
+          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
         </is>
       </c>
     </row>
@@ -6915,17 +6915,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FEED-CHUTE</t>
+          <t>EL-TC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Metal lined transfer chute</t>
+          <t>Adafruit3263 MAX31856</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>TRANSFER_PATH_HOLD</t>
+          <t>PURCHASE_CANDIDATE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>https://www.adafruit.com/product/3263</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
+          <t>Four independent temperature inputs; K probes exact mechanical model unresolved.</t>
         </is>
       </c>
     </row>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GUARDS</t>
+          <t>FASTENERS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Steel cutter containment / chain guards / heat shield</t>
+          <t>Brackets, metal supports,keys,shims,retainers</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SAFETY_GEOMETRY_HOLD</t>
+          <t>HARDWARE_SCHEDULE_HOLD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
+          <t>Not an orderable quantity list; full mechanical fastener closure is outstanding.</t>
         </is>
       </c>
     </row>
@@ -7029,12 +7029,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SAFE-BRAKE</t>
+          <t>FEED-CHUTE</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bus overvoltage/braking protection</t>
+          <t>Metal lined transfer chute</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>REGEN_DESIGN_HOLD</t>
+          <t>TRANSFER_PATH_HOLD</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>PSU sink ability unknown; no regeneration assumption.</t>
+          <t>Complete swept envelope/bridging check and split-print panels before release.</t>
         </is>
       </c>
     </row>
@@ -7086,12 +7086,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SAFE-CONTACT</t>
+          <t>GUARDS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>24V coil DC rated contactor</t>
+          <t>Steel cutter containment / chain guards / heat shield</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7106,12 +7106,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SAFETY_SELECTION_HOLD</t>
+          <t>SAFETY_GEOMETRY_HOLD</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Supplier drawing / capacity confirmation required before procurement</t>
+          <t>PPR-C1 original dimensional design; not an empirical qualification</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
+          <t>Do not operate the open review assembly. Guard geometry still to be detailed.</t>
         </is>
       </c>
     </row>
@@ -7143,12 +7143,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SAFE-FUSE</t>
+          <t>SAFE-BRAKE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Branch and mains fuses / holders</t>
+          <t>Bus overvoltage/braking protection</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CIRCUIT_DESIGN_HOLD</t>
+          <t>REGEN_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
+          <t>PSU sink ability unknown; no regeneration assumption.</t>
         </is>
       </c>
     </row>
@@ -7200,17 +7200,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SAFE-LOCK</t>
+          <t>SAFE-CONTACT</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Coded/positive-opening guard lock</t>
+          <t>24V coil DC rated contactor</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7245,7 +7245,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>Lid and service access, standstill unlock, manual reset.</t>
+          <t>Continuous&gt;=35A DC and fault-current breaking coordinated with fuse.</t>
         </is>
       </c>
     </row>
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SAFE-STOP</t>
+          <t>SAFE-FUSE</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Existing E-stop</t>
+          <t>Branch and mains fuses / holders</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -7277,12 +7277,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OWNED_RATING_VERIFY</t>
+          <t>CIRCUIT_DESIGN_HOLD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -7292,17 +7292,17 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify.</t>
+          <t>Select from actual cable ampacity, DC breaking and inrush. No guessed fuse order.</t>
         </is>
       </c>
     </row>
@@ -7314,17 +7314,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SAFE-THERM</t>
+          <t>SAFE-LOCK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Independent thermal cutoff chain</t>
+          <t>Coded/positive-opening guard lock</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7359,24 +7359,24 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
+          <t>Lid and service access, standstill unlock, manual reset.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>vp1_stage1_3</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AUG_BEARINGS</t>
+          <t>SAFE-STOP</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>west split pillow plus east journal cradle for the r3 auger shaft</t>
+          <t>Existing E-stop</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7386,54 +7386,54 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>steel plate 5 mm</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>OWNED_RATING_VERIFY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>PPR_project_handover_2026-09-20.zip / 08_BOM_COMPONENTS.md</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>C1_INTERFACE_BASELINE</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNQUOTED_NOT_ZERO</t>
+          <t>OWNED_NO_NEW_PURCHASE</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Auger shaft supported at both ends - UNQUOTED</t>
+          <t>Independent hard cut with contactor; contact configuration verify.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>vp1_stage1_3</t>
+          <t>system_requirement</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AUG_SHAFT</t>
+          <t>SAFE-THERM</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; U-shell bore r9.5, nominal BRep gap 1.085 mm</t>
+          <t>Independent thermal cutoff chain</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>steel shaft + steel flight</t>
+          <t>Procurement requirement</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>SAFETY_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>Supplier drawing / capacity confirmation required before procurement</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>C1_INTERFACE_BASELINE</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>UNQUOTED_NOT_ZERO</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; tolerance/runout/heat stack assumed not proven</t>
+          <t>Normally closed manual-reset overtemp plus one-shot protection.</t>
         </is>
       </c>
     </row>
@@ -7485,12 +7485,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AUG_WHEEL</t>
+          <t>AUG_BEARINGS</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>16T worm wheel (REFERENCE geometry, unrated), face x359..365, sector web, teeth cut by discrete hobbing of the worm; keyed Ø6 auger bore</t>
+          <t>west split pillow plus east journal cradle for the r3 auger shaft</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>steel (reference)</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>REFERENCE_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Matched 1.8 mm key and keyway transfer torque to AUG_SHAFT; tooth strength and wear unqualified - UNQUOTED</t>
+          <t>Auger shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7542,12 +7542,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CHUTE_BODY</t>
+          <t>AUG_SHAFT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
+          <t>active auger conveyor: r3 shaft x236..370 at y232/z347.1; RH flight root r3/OD r8, pitch 28.5, four turns x238.5..352.5 with 3 mm swept face; U-shell bore r9.5, nominal BRep gap 1.085 mm</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm + formed trough</t>
+          <t>steel shaft + steel flight</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
+          <t>Conveys +x at -5.4375 rpm for 58 rpm reference M1 via 15/40 gear and 24/12 chain B plus 8:1 worm/wheel; tolerance/runout/heat stack assumed not proven</t>
         </is>
       </c>
     </row>
@@ -7599,12 +7599,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CHUTE_TROUGH_FLOOR_E</t>
+          <t>AUG_WHEEL</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>bolted trough ledge section over the S2 mouth</t>
+          <t>16T worm wheel (REFERENCE geometry, unrated), face x359..365, sector web, teeth cut by discrete hobbing of the worm; keyed Ø6 auger bore</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7614,22 +7614,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>GEOMETRY_PASS</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
+          <t>Matched 1.8 mm key and keyway transfer torque to AUG_SHAFT; tooth strength and wear unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7656,12 +7656,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CROSS_FEED_BEARINGS</t>
+          <t>CHUTE_BODY</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>paired cross-feed and idler journal support with structural rails</t>
+          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>steel plate and journal shells</t>
+          <t>steel sheet 3 mm + formed trough</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7681,14 +7681,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
           <t>VP1-STAGE5</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>VP1-STAGE5</t>
-        </is>
-      </c>
       <c r="I135" t="inlineStr">
         <is>
           <t/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
+          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7713,12 +7713,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CROSS_FEED_GEAR</t>
+          <t>CHUTE_TROUGH_FLOOR_E</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>12T keyed output gear on transverse feed shaft</t>
+          <t>bolted trough ledge section over the S2 mouth</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>GEOMETRY_PASS</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
+          <t>Clearance-cut for the frozen saddle jacket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CROSS_FEED_IDLER</t>
+          <t>CROSS_FEED_BEARINGS</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
+          <t>paired cross-feed and idler journal support with structural rails</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>steel reference gear and shaft</t>
+          <t>steel plate and journal shells</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
+          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHAFT</t>
+          <t>CROSS_FEED_GEAR</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
+          <t>12T keyed output gear on transverse feed shaft</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>steel shaft and welded flight</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
+          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHELL</t>
+          <t>CROSS_FEED_IDLER</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
+          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>formed steel sheet</t>
+          <t>steel reference gear and shaft</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
+          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-A</t>
+          <t>CROSS_FEED_SHAFT</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
+          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7956,22 +7956,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel shaft and welded flight</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>VP1-STAGE1</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
+          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-B</t>
+          <t>CROSS_FEED_SHELL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
+          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8013,22 +8013,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>formed steel sheet</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
+          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>EL_CONTACTOR</t>
+          <t>DRV-CHAIN-A</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>safety contactor</t>
+          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8070,22 +8070,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>24 V coil contactor MPN unselected</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE1</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
         </is>
       </c>
     </row>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>EL_CURRENT_LIMITER</t>
+          <t>DRV-CHAIN-B</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>heater sequencer / current-limit relay bank</t>
+          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8127,24 +8127,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>relay bank MPN unselected</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CONTROL_REFERENCE_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
           <t>VP1-STAGE4</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>VP1-STAGE4</t>
-        </is>
-      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t/>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EL_DIN_RAIL</t>
+          <t>EL_CONTACTOR</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DIN rail 35 mm top-hat x 210</t>
+          <t>safety contactor</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>steel rail</t>
+          <t>24 V coil contactor MPN unselected</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EL_DRIVER_1</t>
+          <t>EL_CURRENT_LIMITER</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M1 branch)</t>
+          <t>heater sequencer / current-limit relay bank</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8241,22 +8241,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>relay bank MPN unselected</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>CONTROL_REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EL_DRIVER_2</t>
+          <t>EL_DIN_RAIL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M2 branch)</t>
+          <t>DIN rail 35 mm top-hat x 210</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>steel rail</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EL_DRIVER_3</t>
+          <t>EL_DRIVER_1</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (winder/puller accessory)</t>
+          <t>stepper/BLDC driver (M1 branch)</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EL_ESTOP_BOX</t>
+          <t>EL_DRIVER_2</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>dual-channel E-stop / lid / service interlock relay box</t>
+          <t>stepper/BLDC driver (M2 branch)</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EL_OVERTEMP_BOX</t>
+          <t>EL_DRIVER_3</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>manual-reset independent overtemperature relay box</t>
+          <t>stepper/BLDC driver (winder/puller accessory)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EL_WIRE_DUCT</t>
+          <t>EL_ESTOP_BOX</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>slotted wiring duct x 210</t>
+          <t>dual-channel E-stop / lid / service interlock relay box</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>PVC duct</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_A</t>
+          <t>EL_OVERTEMP_BOX</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>chain A top-run lid plate</t>
+          <t>manual-reset independent overtemperature relay box</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8583,17 +8583,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_B</t>
+          <t>EL_WIRE_DUCT</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
+          <t>slotted wiring duct x 210</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>PVC duct</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GUARD_LID_INTERLOCK_SEAT</t>
+          <t>GUARD_CHAIN_A</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>hopper-lid interlock switch seat</t>
+          <t>chain A top-run lid plate</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GUARD_S2_RING</t>
+          <t>GUARD_CHAIN_B</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
+          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8796,37 +8796,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>HOPPER_FASTENER_M3</t>
+          <t>GUARD_LID_INTERLOCK_SEAT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>M3 x 12 through-bolt with low-profile head for PC panel to captive steel seam boss</t>
+          <t>hopper-lid interlock switch seat</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>steel metric fastener</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FASTENER_ENVELOPE_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>M3 clearance holes and captive bosses are modeled; bolts/heads not modeled or selected. Head bearing/seal outside taper and torque/preload must be qualified before fabrication; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>HOPPER_PANEL_L</t>
+          <t>GUARD_S2_RING</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>C1 HOPPER.step PC loft cut at world x120, left half with front/rear M3 through-holes</t>
+          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8868,22 +8868,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>polycarbonate FDM shell nominal 3 mm</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>PRINT_DFM_LINER_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Actual CAD bbox 119.258 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
+          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8910,27 +8910,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HOPPER_PANEL_R</t>
+          <t>HOPPER_FASTENER_M3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>C1 HOPPER.step PC loft cut at world x120, right half with front/rear M3 through-holes</t>
+          <t>M3 x 12 through-bolt with low-profile head for PC panel to captive steel seam boss</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>polycarbonate FDM shell nominal 3 mm</t>
+          <t>steel metric fastener</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>PRINT_DFM_LINER_HOLD</t>
+          <t>FASTENER_ENVELOPE_HOLD</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Actual CAD bbox 117 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
+          <t>M3 clearance holes and captive bosses are modeled; bolts/heads not modeled or selected. Head bearing/seal outside taper and torque/preload must be qualified before fabrication; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HOPPER_SEAM_FRONT</t>
+          <t>HOPPER_PANEL_L</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>40 x 39 x 1.5 mm sloping steel upper front seam strap with four M3 clearance holes and integral captive hex bosses</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, left half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>steel strip and welded captive bosses</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>SEAM_AND_LINER_HOLD</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
+          <t>Actual CAD bbox 119.258 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HOPPER_SEAM_REAR</t>
+          <t>HOPPER_PANEL_R</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>40 x 39 x 1.5 mm sloping steel upper rear seam strap with four M3 clearance holes and integral captive hex bosses</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, right half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>steel strip and welded captive bosses</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>SEAM_AND_LINER_HOLD</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
+          <t>Actual CAD bbox 117 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PDL_BEARINGS</t>
+          <t>HOPPER_SEAM_FRONT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper front seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9096,22 +9096,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>steel plate 5 mm</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Mounted on the support-plate bosses - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PDL_CHAIN</t>
+          <t>HOPPER_SEAM_REAR</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper rear seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9153,22 +9153,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9195,12 +9195,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PDL_FEED_GEAR</t>
+          <t>PDL_BEARINGS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
+          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
+          <t>Mounted on the support-plate bosses - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9252,12 +9252,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PDL_SHAFT</t>
+          <t>PDL_CHAIN</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
+          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>steel rod C45 candidate</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
+          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PDL_SPROCKET</t>
+          <t>PDL_FEED_GEAR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
+          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
+          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PDL_WORM</t>
+          <t>PDL_SHAFT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
+          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>steel (reference)</t>
+          <t>steel rod C45 candidate</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>REFERENCE_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
+          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PULL_FRAME</t>
+          <t>PDL_SPROCKET</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
+          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9438,22 +9438,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
+          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>PDL_WORM</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9495,22 +9495,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>PULL_FRAME</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
+          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel plate 5 mm + 3 mm</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -9562,12 +9562,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9609,12 +9609,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>steel; M5 screw</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9651,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PULL_NIP_STOP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9708,37 +9708,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>S1_BELT</t>
+          <t>PULL_ROLLER_ADJ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>polymer belt with steel-supported drums</t>
+          <t>steel; M5 screw</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Friction and tension unrated; UNQUOTED</t>
+          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9765,12 +9765,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>S1_BELT_BEARINGS</t>
+          <t>PULL_ROLLER_FIXED</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>four belt shaft support rings in the side rails</t>
+          <t>puller drive roller dia 20 x 22</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9780,22 +9780,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel; knurl or rubber per TPU grip</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Bearing selection and loads unqualified; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9822,22 +9822,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S1_BELT_CHAIN</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>#35 chain from S1B 24T to west belt 12T</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>ANSI35 steel chain</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Tension and strength unrated; UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>S1_BELT_DRIVE</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>steel shaft and drums</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>S1_BELT_FOLLOWER</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>12T sprocket on the west belt driver</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9993,12 +9993,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>S1_BELT_IDLER</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>steel journals and drums</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Two independent journal halves; UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>S1_SWEEP_BEARINGS</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>two separated sweep bearing rings in the pan rails</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_N</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>12T gear on the north east belt idler</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_S</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>12T gear on the south east belt idler</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_N</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>12T gear on the north sweep shaft</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10278,12 +10278,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_S</t>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>12T gear on the south sweep shaft</t>
+          <t>12T gear on the south east belt idler</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S1_SWEEP_NORTH</t>
+          <t>S1_SWEEP_GEAR_N</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
+          <t>12T gear on the north sweep shaft</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S1_SWEEP_SOUTH</t>
+          <t>S1_SWEEP_GEAR_S</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
+          <t>12T gear on the south sweep shaft</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BEARINGS</t>
+          <t>S1_SWEEP_NORTH</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>two central idler support rings</t>
+          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BELT</t>
+          <t>S1_SWEEP_SOUTH</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
+          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>polymer belt</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Screw pickup unproven; UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_IDLER</t>
+          <t>S1_TRANSFER_BEARINGS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>central east r2.3 idler at x260</t>
+          <t>two central idler support rings</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>steel drum</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>S1_TRANSFER_BELT</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10635,22 +10635,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>polymer belt</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>Screw pickup unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>S1_TRANSFER_IDLER</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>central east r2.3 idler at x260</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10692,22 +10692,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel drum</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>WIND_FLANGE_L</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -10791,12 +10791,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>WIND_FLANGE_R</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10806,22 +10806,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10848,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>WIND_MOTOR_REF</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>spool gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -10905,12 +10905,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_SPOOL_BEARINGS</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel plate 5 mm + bearing seats</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10930,12 +10930,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_SPOOL_DRUM</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>spool drum dia 70 x 58</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel tube or printed polymer</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_SPOOL_SHAFT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>spool shaft dia 16 x 95</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>C45 candidate</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11076,50 +11076,164 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C197" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
+      <c r="G197" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
+      <c r="H197" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
+      <c r="I197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="K197" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -5324,7 +5324,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Steel screen receiver with inset shoulder</t>
+          <t>Steel receiver190x48 top /Ø20 neck</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Original 190x48 mouth at z218, outer envelope z145..218; inset at z210 has inner x245..360,y255.5..294.5, covering the nominal S2 screen-bore columns without touching the screen edge at z215.2. Lower Ø13 clear octagonal throat at x299,y275,z145 with Ø18 outer neck z145..160. Weld to separate steel saddle at z145; fasteners, sealing, thermal isolation and fabrication DFM remain HOLD. No material-flow or physical-release claim.</t>
+          <t>Original 190x48 mouth at z218, outer envelope z145..218; inset at z210 has inner x247..358,y255.5..294.5, enclosing nominal screen bores. Lower Ø13 clear octagonal throat at x299,y275,z145 with Ø20 outer neck z145..160 and steel saddle; fasteners, weld, sealing, thermal fit and fabrication DFM remain HOLD. No material-flow or physical-release claim.</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CROSS_FEED_BEARINGS</t>
+          <t>COOL-DUCT</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>paired cross-feed and idler journal support with structural rails</t>
+          <t>adjustable cooling duct: rails + sliding baffle (100 mm travel, 50..250 mm ducted length) over COOL-TRAY</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7785,22 +7785,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>steel plate and journal shells</t>
+          <t>steel sheet 3 mm rails + baffle</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>COOLING_CAPACITY_UNRATED</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CROSS_FEED_GEAR</t>
+          <t>COOL-FAN-3_REF</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>12T keyed output gear on transverse feed shaft</t>
+          <t>third 80 mm fan reference on cooling baffle (9RA0824H1001 class)</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7842,22 +7842,22 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>80 mm 24 V fan MPN unselected</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>FAN_UNSELECTED</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
+          <t>UNRATED 8 W estimate admitted by 500 W allocator; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CROSS_FEED_IDLER</t>
+          <t>CROSS_FEED_BEARINGS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
+          <t>paired cross-feed and idler journal support with structural rails</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>steel reference gear and shaft</t>
+          <t>steel plate and journal shells</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
+          <t>BRep-supported reference geometry; wear and load unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHAFT</t>
+          <t>CROSS_FEED_GEAR</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
+          <t>12T keyed output gear on transverse feed shaft</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>steel shaft and welded flight</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
+          <t>1:1 from PDL through idler; tooth contact and torque rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CROSS_FEED_SHELL</t>
+          <t>CROSS_FEED_IDLER</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
+          <t>12T integral idler and supported journal between PDL and transverse feed gears</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>formed steel sheet</t>
+          <t>steel reference gear and shaft</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
+          <t>Two external meshes preserve rotation sign; journal rating unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8055,12 +8055,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-A</t>
+          <t>CROSS_FEED_SHAFT</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
+          <t>RH helical screw on y-axis x357/z328 with 9 mm pitch; reduced-radius powered tail to y260.5</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8070,22 +8070,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel shaft and welded flight</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>VP1-STAGE1</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
+          <t>Powered tail overlaps S2 mouth y255 by 5.502 mm; actual fragment handoff unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>DRV-CHAIN-B</t>
+          <t>CROSS_FEED_SHELL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
+          <t>U cradle with rotor-relieved outer metal shelf past S2 mouth</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8127,22 +8127,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>formed steel sheet</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>VP1-ADR-002</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
+          <t>Outer shelf y255..258 supports the handoff without entering swept rotor sector; material transfer unproven - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EL_CONTACTOR</t>
+          <t>DRV-CHAIN-A</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>safety contactor</t>
+          <t>#35 roller chain cut to 896 mm (94 links; chain A: jackshaft 24T -&gt; S1 shaft A 24T)</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8184,22 +8184,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>24 V coil contactor MPN unselected</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-ADR-002</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE1</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (drive_geometry.json chain_lengths.A=896.0). UNQUOTED: not 0 - the 100000 KRW soft limit applies to quoted lines only</t>
         </is>
       </c>
     </row>
@@ -8226,12 +8226,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EL_CURRENT_LIMITER</t>
+          <t>DRV-CHAIN-B</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>heater sequencer / current-limit relay bank</t>
+          <t>#35 roller chain cut to 724 mm (76 links; chain B: jackshaft 24T -&gt; S2 12T, ADR-002 rev B)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -8241,24 +8241,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>relay bank MPN unselected</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CONTROL_REFERENCE_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
+          <t>VP1-ADR-002</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
           <t>VP1-STAGE4</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>VP1-STAGE4</t>
-        </is>
-      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t/>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
+          <t>Cut length from tangent+pitch-arc geometry (chain_lengths.B=723.9). UNQUOTED: not 0</t>
         </is>
       </c>
     </row>
@@ -8283,12 +8283,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EL_DIN_RAIL</t>
+          <t>EL_CONTACTOR</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DIN rail 35 mm top-hat x 210</t>
+          <t>safety contactor</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>steel rail</t>
+          <t>24 V coil contactor MPN unselected</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8340,12 +8340,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EL_DRIVER_1</t>
+          <t>EL_CURRENT_LIMITER</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M1 branch)</t>
+          <t>heater sequencer / current-limit relay bank</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -8355,22 +8355,22 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>relay bank MPN unselected</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>CONTROL_REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8385,7 +8385,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8397,12 +8397,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EL_DRIVER_2</t>
+          <t>EL_DIN_RAIL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (M2 branch)</t>
+          <t>DIN rail 35 mm top-hat x 210</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>24 V driver MPN unselected</t>
+          <t>steel rail</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8454,12 +8454,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EL_DRIVER_3</t>
+          <t>EL_DRIVER_1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>stepper/BLDC driver (winder/puller accessory)</t>
+          <t>stepper/BLDC driver (M1 branch)</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EL_ESTOP_BOX</t>
+          <t>EL_DRIVER_2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>dual-channel E-stop / lid / service interlock relay box</t>
+          <t>stepper/BLDC driver (M2 branch)</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EL_OVERTEMP_BOX</t>
+          <t>EL_DRIVER_3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>manual-reset independent overtemperature relay box</t>
+          <t>stepper/BLDC driver (winder/puller accessory)</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>relay box MPN unselected</t>
+          <t>24 V driver MPN unselected</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SAFETY_HARDWARE_REQUIRED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EL_WIRE_DUCT</t>
+          <t>EL_ESTOP_BOX</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>slotted wiring duct x 210</t>
+          <t>dual-channel E-stop / lid / service interlock relay box</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8640,12 +8640,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PVC duct</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8682,12 +8682,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_A</t>
+          <t>EL_OVERTEMP_BOX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>chain A top-run lid plate</t>
+          <t>manual-reset independent overtemperature relay box</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>relay box MPN unselected</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>SAFETY_HARDWARE_REQUIRED</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GUARD_CHAIN_B</t>
+          <t>EL_WIRE_DUCT</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
+          <t>slotted wiring duct x 210</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -8754,17 +8754,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>PVC duct</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GUARD_LID_INTERLOCK_SEAT</t>
+          <t>GAUGE_CONTACT_A</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>hopper-lid interlock switch seat</t>
+          <t>lever-contact diameter axis: horizontal spring lever + Hall probe head + anvil (candidate sensor, S1/S2 reference class)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -8811,22 +8811,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>lever steel + Hall probe + magnet + spring</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>SENSOR_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>contact compliance and TPU deformation UNRATED; coexistence with optical axis is for comparison not dual purchase; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8853,12 +8853,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>GUARD_S2_RING</t>
+          <t>GAUGE_FRAME</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
+          <t>diameter gauge mounting straps + wall spacers inside COOL-TRAY exit section (x801..807/816..818, bolted to tray walls)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -8868,22 +8868,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>steel plate 3 mm</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>CONTAINMENT_UNRATED</t>
+          <t>GAUGE_ACCURACY_UNRATED</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8910,37 +8910,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HOPPER_FASTENER_M3</t>
+          <t>GAUGE_GUIDES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>M3 x 12 through-bolt with low-profile head for PC panel to captive steel seam boss</t>
+          <t>V-guide roller pair + support axles on the filament line at gauge plane x=809</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>steel metric fastener</t>
+          <t>steel rollers dia 8/11 + axles dia 2.4</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FASTENER_ENVELOPE_HOLD</t>
+          <t>GAUGE_ACCURACY_UNRATED</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>M3 clearance holes and captive bosses are modeled; bolts/heads not modeled or selected. Head bearing/seal outside taper and torque/preload must be qualified before fabrication; UNQUOTED</t>
+          <t>guide contact force unmeasured; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8967,12 +8967,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HOPPER_PANEL_L</t>
+          <t>GAUGE_OPTICAL_B</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>C1 HOPPER.step PC loft cut at world x120, left half with front/rear M3 through-holes</t>
+          <t>open-optics diameter axis: LED emitter + line sensor receiver pair at 90 deg to contact axis (candidate sensor, S4 reference class)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -8982,22 +8982,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>polycarbonate FDM shell nominal 3 mm</t>
+          <t>LED emitter + line sensor + apertures</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>PRINT_DFM_LINER_HOLD</t>
+          <t>SENSOR_SELECTION_HOLD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Actual CAD bbox 119.258 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
+          <t>transparent/TPU stock accuracy unverified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9024,12 +9024,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>HOPPER_PANEL_R</t>
+          <t>GAUGE_REF_STANDARD</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>C1 HOPPER.step PC loft cut at world x120, right half with front/rear M3 through-holes</t>
+          <t>removable pin-gauge holder with 1.50/1.75/2.00 mm precision pins (on-machine calibration artifact)</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -9039,22 +9039,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>polycarbonate FDM shell nominal 3 mm</t>
+          <t>precision ground pins + steel holder</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PRINT_DFM_LINER_HOLD</t>
+          <t>CALIBRATION_ARTIFACT_UNRATED</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Actual CAD bbox 117 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
+          <t>pin grade + micrometer round-trip U95&lt;=0.01mm is physical-test work; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HOPPER_SEAM_FRONT</t>
+          <t>GUARD_CHAIN_A</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>40 x 39 x 1.5 mm sloping steel upper front seam strap with four M3 clearance holes and integral captive hex bosses</t>
+          <t>chain A top-run lid plate</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -9096,22 +9096,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>steel strip and welded captive bosses</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SEAM_AND_LINER_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HOPPER_SEAM_REAR</t>
+          <t>GUARD_CHAIN_B</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>40 x 39 x 1.5 mm sloping steel upper rear seam strap with four M3 clearance holes and integral captive hex bosses</t>
+          <t>chain B outer guard plate set (continuous; ADR-002 rev B re-route)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -9153,22 +9153,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>steel strip and welded captive bosses</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SEAM_AND_LINER_HOLD</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-SPLIT</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>VP1-HOPPER-GEOMETRY</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9195,12 +9195,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PDL_BEARINGS</t>
+          <t>GUARD_LID_INTERLOCK_SEAT</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
+          <t>hopper-lid interlock switch seat</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -9210,22 +9210,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>steel plate 5 mm</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Mounted on the support-plate bosses - UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9252,12 +9252,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PDL_CHAIN</t>
+          <t>GUARD_S2_RING</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
+          <t>S2 rotor ring guard (annular sector r 90..94 over 20..114 deg)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9267,22 +9267,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>ANSI35 steel roller chain p=9.525</t>
+          <t>steel plate 3 mm</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>CONTAINMENT_UNRATED</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
+          <t>Guard plate thickness unrated; service sweep verified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9309,37 +9309,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PDL_FEED_GEAR</t>
+          <t>HOPPER_FASTENER_M3</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
+          <t>M3 x 12 through-bolt with low-profile head for PC panel to captive steel seam boss</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>steel reference gear</t>
+          <t>steel metric fastener</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>FASTENER_ENVELOPE_HOLD</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
+          <t>M3 clearance holes and captive bosses are modeled; bolts/heads not modeled or selected. Head bearing/seal outside taper and torque/preload must be qualified before fabrication; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PDL_SHAFT</t>
+          <t>HOPPER_PANEL_L</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, left half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9381,22 +9381,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>steel rod C45 candidate</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
+          <t>Actual CAD bbox 119.258 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9423,12 +9423,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PDL_SPROCKET</t>
+          <t>HOPPER_PANEL_R</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
+          <t>C1 HOPPER.step PC loft cut at world x120, right half with front/rear M3 through-holes</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -9438,22 +9438,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>polycarbonate FDM shell nominal 3 mm</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>PRINT_DFM_LINER_HOLD</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
+          <t>Actual CAD bbox 117 x 162.2 x 55.497 mm; print orientation/adhesion/infill and assembled joint strength unqualified; historical HOPPER_001 removed from active quantity; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PDL_WORM</t>
+          <t>HOPPER_SEAM_FRONT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper front seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -9495,22 +9495,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>steel (reference)</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>REFERENCE_UNRATED</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9537,12 +9537,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PULL_FRAME</t>
+          <t>HOPPER_SEAM_REAR</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
+          <t>40 x 39 x 1.5 mm sloping steel upper rear seam strap with four M3 clearance holes and integral captive hex bosses</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -9552,22 +9552,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>steel strip and welded captive bosses</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>SEAM_AND_LINER_HOLD</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-HOPPER-SPLIT</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-HOPPER-GEOMETRY</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
+          <t>Wall-face support z456..495 across x120 split; not the C1 unmodeled lower steel safety liner; weld and bolt loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9594,12 +9594,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>PDL_BEARINGS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>two split pillow posts carrying the worm shaft at x353..365, y204..210/352..358</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -9609,22 +9609,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 5 mm</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Mounted on the support-plate bosses - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9651,12 +9651,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>PDL_CHAIN</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
+          <t>#35 roller chain, 35 links incl. offset link; S2 12T second band to PDL_SPROCKET at x362, 1:1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -9666,22 +9666,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>ANSI35 steel roller chain p=9.525</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Nominal333.375 mm versus geometric332.734 mm; 0.641 mm length surplus. Offset-link strength and tension adjustment unqualified; no quote - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9708,12 +9708,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>PDL_FEED_GEAR</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
+          <t>12T keyed spur on worm shaft feeding orthogonal screw train</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -9723,22 +9723,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>steel; M5 screw</t>
+          <t>steel reference gear</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
+          <t>Tooth strength and keyed fit unqualified - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9765,12 +9765,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PDL_SHAFT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>trough worm shaft dia 10 x 188 (r5, y204..392, x362, z374.5), dia 12 keyed chain shoulder y376..392</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -9780,22 +9780,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel rod C45 candidate</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Carries the RH 2-start worm; keyed 12T sprocket takes 1:1 PDL_CHAIN drive from the S2 12T sprocket - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9822,22 +9822,22 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>S1_BELT</t>
+          <t>PDL_SPROCKET</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
+          <t>worm-shaft drive sprocket 12T bore 12 mm with keyed hub on shaft shoulder</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>polymer belt with steel-supported drums</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Friction and tension unrated; UNQUOTED</t>
+          <t>Bore r6 on y376..392 shaft shoulder r6 with 1.8 mm key in matched slot; torque fit and chain rating UNRATED - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>S1_BELT_BEARINGS</t>
+          <t>PDL_WORM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>four belt shaft support rings in the side rails</t>
+          <t>RH 2-start worm (REFERENCE geometry, unrated): root r6/pitch r6.75/OD r7.5, lead angle 23.3 deg, length 20 (y220..240), keyed Ø10 shaft bore</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel (reference)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>REFERENCE_UNRATED</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Bearing selection and loads unqualified; UNQUOTED</t>
+          <t>Matched 1.8 mm key and keyway transfer torque from PDL_SHAFT; tooth mesh and loads remain unrated - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9936,12 +9936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>S1_BELT_CHAIN</t>
+          <t>PULL_FRAME</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>#35 chain from S1B 24T to west belt 12T</t>
+          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9951,22 +9951,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ANSI35 steel chain</t>
+          <t>steel plate 5 mm + 3 mm</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Tension and strength unrated; UNQUOTED</t>
+          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -9993,12 +9993,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>S1_BELT_DRIVE</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10008,22 +10008,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>steel shaft and drums</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>S1_BELT_FOLLOWER</t>
+          <t>PULL_NIP_STOP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>12T sprocket on the west belt driver</t>
+          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10065,22 +10065,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>S1_BELT_IDLER</t>
+          <t>PULL_ROLLER_ADJ</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10122,22 +10122,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel journals and drums</t>
+          <t>steel; M5 screw</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Two independent journal halves; UNQUOTED</t>
+          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>S1_SWEEP_BEARINGS</t>
+          <t>PULL_ROLLER_FIXED</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>two separated sweep bearing rings in the pan rails</t>
+          <t>puller drive roller dia 20 x 22</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel; knurl or rubber per TPU grip</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10221,22 +10221,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_N</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>12T gear on the north east belt idler</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_S</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>12T gear on the south east belt idler</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_N</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>12T gear on the north sweep shaft</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_S</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>12T gear on the south sweep shaft</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S1_SWEEP_NORTH</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S1_SWEEP_SOUTH</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BEARINGS</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>two central idler support rings</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BELT</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>polymer belt</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>Screw pickup unproven; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_IDLER</t>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>central east r2.3 idler at x260</t>
+          <t>12T gear on the south east belt idler</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>steel drum</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>S1_SWEEP_GEAR_N</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>12T gear on the north sweep shaft</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10749,22 +10749,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10791,12 +10791,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>S1_SWEEP_GEAR_S</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>12T gear on the south sweep shaft</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10806,22 +10806,22 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10848,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>S1_SWEEP_NORTH</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10863,22 +10863,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10905,12 +10905,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>S1_SWEEP_SOUTH</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10920,22 +10920,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>S1_TRANSFER_BEARINGS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>two central idler support rings</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10977,22 +10977,22 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11019,12 +11019,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>S1_TRANSFER_BELT</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11034,22 +11034,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>polymer belt</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Screw pickup unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>S1_TRANSFER_IDLER</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>central east r2.3 idler at x260</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11091,22 +11091,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel drum</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>SERVICE-HOPPER</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>SWAP reference-feedstock hopper on FEED-BUF saddle interface (x282..316 y251..299 z145..218); replaces buffer stack for reference runs</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11148,22 +11148,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>SWAP_PART_NO_INTERLOCK</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>NOT in production assembly; no interlock credit</t>
         </is>
       </c>
     </row>
@@ -11190,50 +11190,506 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
+          <t>WIND_FLANGE_L</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>spool flange dia 200 x 3 mm</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm screening candidate</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>WIND_FLANGE_R</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>spool flange dia 200 x 3 mm</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>steel plate 3 mm screening candidate</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>WIND_MOTOR_REF</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>spool gearmotor reference (not selected)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>24 V gearmotor MPN unselected</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>MOTOR_UNSELECTED</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_BEARINGS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>steel plate 5 mm + bearing seats</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>VP1-STAGE4</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_DRUM</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>spool drum dia 70 x 58</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>steel tube or printed polymer</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>WIND_SPOOL_SHAFT</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>spool shaft dia 16 x 95</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>C45 candidate</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>slip tensioner post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
+      <c r="H205" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
+      <c r="I205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="K205" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>welded S1-&gt;S2 transfer chute with sealed pan, active screw-conveyor trough and east fallaway</t>
+          <t>welded S1-&gt;S2 transfer chute with sweep-flight reliefs, central transfer belt and east auger receiver</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>BRep geometry and digital flow only; material transport and containment are not physically qualified - UNQUOTED</t>
+          <t>Static BRep clearance only; previous native S1 pickup 10/22 and auger advance 1/22 on older STEP; no new same-particle run; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>adjustable cooling duct: rails + sliding baffle (100 mm travel, 50..250 mm ducted length) over COOL-TRAY</t>
+          <t>vented sliding hood on rails with 100 mm travel over COOL-TRAY</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm rails + baffle</t>
+          <t>steel sheet 3 mm rails + hood</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>COOL-TRAY south wall gains two 78x21 ports and hood top fan gets open aperture; 50..250 mm effective cooling length remains uncalibrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>third 80 mm fan reference on cooling baffle (9RA0824H1001 class)</t>
+          <t>separate 80x80x38 open-ring third fan envelope on sliding hood</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -7872,7 +7872,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>UNRATED 8 W estimate admitted by 500 W allocator; UNQUOTED</t>
+          <t>8 W sensitivity estimate not rated; no PWM assumed; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Host-tested firmware excludes simultaneous heater bands and rejects demand above 792 W; independent electrical interlock and component ratings still required - UNQUOTED</t>
+          <t>Host-tested firmware excludes simultaneous heater bands and refuses demands above 500 W modeled cap; independent electrical interlock and component ratings still required - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>diameter gauge mounting straps + wall spacers inside COOL-TRAY exit section (x801..807/816..818, bolted to tray walls)</t>
+          <t>diameter gauge mounting straps + wall spacers inside COOL-TRAY exit section (x801..807)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>puller side plates + base + fixed-roller bearing seats + carriage guide slots</t>
+          <t>puller base and side plates with bored Ø8.4 axle seats and east bearing web</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Positive stop 1.5 mm and adjustable open nip to 3.0 mm; spring carriage grips nominal 1.75 mm filament - UNQUOTED</t>
+          <t>Ø20 rollers center the filament 11 mm inboard of both roller ends; bearing selection and carriage linear guide still HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>nip positive-stop cam block (1.5 mm minimum, 3.0 mm open)</t>
+          <t>underside seat at 1.5 mm roller nip; touches frame/carriage without penetration</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Stop attachment and open setting hardware unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage (guide posts, coil springs, cam stop)</t>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage and guide-post envelopes</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel; M5 screw</t>
+          <t>steel + springs unselected</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Spring-loaded carrier grips 1.5-2.0 mm filament (1.75 nominal, design/parameters.json filament_mm); cam stop range 1.5..3.0 mm - UNQUOTED</t>
+          <t>At modeled minimum gap 1.5 mm the 1.75 mm strand intersects both compliant roller envelopes; actual spring force and guide travel not rated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 feeding the central lane</t>
+          <t>north transverse screw x224 y235.5..359 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>Swept flight reaches previously stranded Ø3 mm envelope near x223/z336.5; actual same-particle pickup untested; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10910,7 +10910,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 feeding the central lane</t>
+          <t>south transverse screw x224 y127..228.5 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Dynamic side-belt pickup under verification; UNQUOTED</t>
+          <t>Floor relief provides swept clearance; flake capture and torque not proven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x260 inside the two side loops</t>
+          <t>central 17 mm tread from x80 to x270 inside two side loops</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Screw pickup unproven; UNQUOTED</t>
+          <t>Extended drum and ramp towards auger inlet; traction and throughflow unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>central east r2.3 idler at x260</t>
+          <t>central east r2.05/2.45 idler at x270</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SWAP reference-feedstock hopper on FEED-BUF saddle interface (x282..316 y251..299 z145..218); replaces buffer stack for reference runs</t>
+          <t>SWAP hollow side-inlet for reference material on FEED-BUF saddle; not in production assembly</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>NOT in production assembly; no interlock credit</t>
+          <t>S2 off; saddle seal/fasteners and flow remain HOLD; no interlock credit; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11190,12 +11190,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>WIND_CLUTCH_REF</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>keyed collar + spring envelope + friction washer between driven shaft and loose spool flange</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11205,22 +11205,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel collar + friction pad + spring reference</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TORQUE_LIMIT_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>Axial preload/retention and 70 Nmm sensitivity value not physically designed or rated; torque transmission and costs HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>WIND_FLANGE_L</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11304,12 +11304,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>WIND_FLANGE_R</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11319,12 +11319,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>WIND_MOTOR_REF</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>spool gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11376,22 +11376,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>WIND_SPOOL_BEARINGS</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>spool drum dia 70 x 58</t>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>steel tube or printed polymer</t>
+          <t>steel plate 5 mm + bearing seats</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11475,12 +11475,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_SPOOL_DRUM</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 95</t>
+          <t>spool steel drum dia 70 x 58 with loose shaft bore; weld to steel flanges before winding</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel tube candidate</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Flange seam and balance unqualified; printed drum would require separate fastener design; friction clutch drives flange rather than loose bore; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_SPOOL_SHAFT</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>slip tensioner post + wrap arm</t>
+          <t>spool shaft dia 16 x 98 with keyed clutch collar seat</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>C45 candidate</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Shaft bearing and key torque rating HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11589,12 +11589,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_TENSIONER</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>filament path-buffer post + wrap arm</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TENSION_UNRATED</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Not a calibrated torque limiter; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11646,50 +11646,107 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G206" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H206" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
+      <c r="I206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K206" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -9936,12 +9936,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PULL_FRAME</t>
+          <t>PULL_COOL_MOUNT</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>puller base and side plates with bored Ø8.4 axle seats and east bearing web</t>
+          <t>rear-frame steel tube rack with tray ledge and puller fastener holes</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>steel tube + plate/bar candidate</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>NIP_SUPPORT_HOLD</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>Ø20 rollers center the filament 11 mm inboard of both roller ends; bearing selection and carriage linear guide still HOLD; UNQUOTED</t>
+          <t>Contacts rear FR-2040-400_002, COOL-TRAY_001 underside and PULL_FRAME base; bolts, welds, tray connection and load ratings unselected; unquoted NOT zero</t>
         </is>
       </c>
     </row>
@@ -9993,12 +9993,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>PULL_FRAME</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>puller base and side plates with bored Ø8.4 axle seats and east bearing web</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10008,22 +10008,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 5 mm + 3 mm</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>Ø20 rollers center the filament 11 mm inboard of both roller ends; bearing selection and carriage linear guide still HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>underside seat at 1.5 mm roller nip; touches frame/carriage without penetration</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10065,22 +10065,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>Stop attachment and open setting hardware unqualified; UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -10107,12 +10107,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>PULL_NIP_STOP</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage and guide-post envelopes</t>
+          <t>underside seat at 1.5 mm roller nip; touches frame/carriage without penetration</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel + springs unselected</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>At modeled minimum gap 1.5 mm the 1.75 mm strand intersects both compliant roller envelopes; actual spring force and guide travel not rated; UNQUOTED</t>
+          <t>Stop attachment and open setting hardware unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PULL_ROLLER_ADJ</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>puller adjustable roller dia 20 + spring-loaded carriage and guide-post envelopes</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel + springs unselected</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>At modeled minimum gap 1.5 mm the 1.75 mm strand intersects both compliant roller envelopes; actual spring force and guide travel not rated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10221,37 +10221,37 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>S1_BELT</t>
+          <t>PULL_ROLLER_FIXED</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
+          <t>puller drive roller dia 20 x 22</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>polymer belt with steel-supported drums</t>
+          <t>steel; knurl or rubber per TPU grip</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Friction and tension unrated; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10278,22 +10278,22 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S1_BELT_BEARINGS</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>four belt shaft support rings in the side rails</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Bearing selection and loads unqualified; UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S1_BELT_CHAIN</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>#35 chain from S1B 24T to west belt 12T</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>ANSI35 steel chain</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Tension and strength unrated; UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S1_BELT_DRIVE</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>steel shaft and drums</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S1_BELT_FOLLOWER</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>12T sprocket on the west belt driver</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S1_BELT_IDLER</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>steel journals and drums</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>Two independent journal halves; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S1_SWEEP_BEARINGS</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>two separated sweep bearing rings in the pan rails</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_N</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>12T gear on the north east belt idler</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_S</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>12T gear on the south east belt idler</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_N</t>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>12T gear on the north sweep shaft</t>
+          <t>12T gear on the south east belt idler</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_S</t>
+          <t>S1_SWEEP_GEAR_N</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>12T gear on the south sweep shaft</t>
+          <t>12T gear on the north sweep shaft</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>S1_SWEEP_NORTH</t>
+          <t>S1_SWEEP_GEAR_S</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 radius 7.2 flight feeding central lane</t>
+          <t>12T gear on the south sweep shaft</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Swept flight reaches previously stranded Ø3 mm envelope near x223/z336.5; actual same-particle pickup untested; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10905,12 +10905,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S1_SWEEP_SOUTH</t>
+          <t>S1_SWEEP_NORTH</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 radius 7.2 flight feeding central lane</t>
+          <t>north transverse screw x224 y235.5..359 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Floor relief provides swept clearance; flake capture and torque not proven; UNQUOTED</t>
+          <t>Swept flight reaches previously stranded Ø3 mm envelope near x223/z336.5; actual same-particle pickup untested; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BEARINGS</t>
+          <t>S1_SWEEP_SOUTH</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>two central idler support rings</t>
+          <t>south transverse screw x224 y127..228.5 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Floor relief provides swept clearance; flake capture and torque not proven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11019,12 +11019,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BELT</t>
+          <t>S1_TRANSFER_BEARINGS</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x270 inside two side loops</t>
+          <t>two central idler support rings</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>polymer belt</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Extended drum and ramp towards auger inlet; traction and throughflow unproven; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_IDLER</t>
+          <t>S1_TRANSFER_BELT</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>central east r2.05/2.45 idler at x270</t>
+          <t>central 17 mm tread from x80 to x270 inside two side loops</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>steel drum</t>
+          <t>polymer belt</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Extended drum and ramp towards auger inlet; traction and throughflow unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11133,12 +11133,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SERVICE-HOPPER</t>
+          <t>S1_TRANSFER_IDLER</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>SWAP hollow side-inlet for reference material on FEED-BUF saddle; not in production assembly</t>
+          <t>central east r2.05/2.45 idler at x270</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11148,22 +11148,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm</t>
+          <t>steel drum</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SWAP_PART_NO_INTERLOCK</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>VP1-STAGE6</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>VP1-STAGE6</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>S2 off; saddle seal/fasteners and flow remain HOLD; no interlock credit; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11190,12 +11190,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>WIND_CLUTCH_REF</t>
+          <t>SERVICE-HOPPER</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>keyed collar + spring envelope + friction washer between driven shaft and loose spool flange</t>
+          <t>SWAP hollow side-inlet for reference material on FEED-BUF saddle; not in production assembly</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11205,22 +11205,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>steel collar + friction pad + spring reference</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>TORQUE_LIMIT_UNQUALIFIED</t>
+          <t>SWAP_PART_NO_INTERLOCK</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>Axial preload/retention and 70 Nmm sensitivity value not physically designed or rated; torque transmission and costs HOLD; UNQUOTED</t>
+          <t>S2 off; saddle seal/fasteners and flow remain HOLD; no interlock credit; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11247,12 +11247,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>WIND_CLUTCH_REF</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>keyed collar + spring envelope + friction washer between driven shaft and loose spool flange</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11262,22 +11262,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel collar + friction pad + spring reference</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TORQUE_LIMIT_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>Axial preload/retention and 70 Nmm sensitivity value not physically designed or rated; torque transmission and costs HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>WIND_FLANGE_L</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>WIND_FLANGE_R</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>WIND_MOTOR_REF</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>spool gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11433,22 +11433,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -11475,12 +11475,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>WIND_MOUNT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>spool steel drum dia 70 x 58 with loose shaft bore; weld to steel flanges before winding</t>
+          <t>steel cantilever with front-profile face plate, two bearing rails and motor bed</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>steel tube candidate</t>
+          <t>steel plate/bar 4-8 mm + M5 candidate clearances</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>WINDER_JOINT_HOLD</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>Flange seam and balance unqualified; printed drum would require separate fastener design; friction clutch drives flange rather than loose bore; UNQUOTED</t>
+          <t>BRep face contact to FR-2020-400_001 and bearing/motor seats; profile slot, fastener/weld sizes, cantilever stiffness, vibration and guard HOLD; no quote - NOT 0</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_SPOOL_BEARINGS</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 98 with keyed clutch collar seat</t>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel plate 5 mm + bearing seats</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Shaft bearing and key torque rating HOLD; UNQUOTED</t>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11589,12 +11589,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_SPOOL_DRUM</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>filament path-buffer post + wrap arm</t>
+          <t>spool dia 70 x 58 steel tube with 2 mm wall and two 3 mm internal annular webs; weld to steel flanges before winding</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11604,22 +11604,22 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>steel tube + steel webs candidate</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>TENSION_UNRATED</t>
+          <t>WINDER_UNRATED</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Not a calibrated torque limiter; UNQUOTED</t>
+          <t>Web-to-tube and flange seams and balance unqualified; loose Ø17 web bores clear Ø16 shaft; friction clutch drives flange; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11646,12 +11646,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_SPOOL_SHAFT</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>spool shaft dia 16 x 98 with keyed clutch collar seat</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>C45 candidate</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Shaft bearing and key torque rating HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11703,50 +11703,164 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>filament path-buffer post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>TENSION_UNRATED</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Not a calibrated torque limiter; UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
+      <c r="I208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="K208" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -11292,7 +11292,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Axial preload/retention and 70 Nmm sensitivity value not physically designed or rated; torque transmission and costs HOLD; UNQUOTED</t>
+          <t>Separate groove-backed retention closes candidate axial path; actual spring compression/preload and 70 Nmm sensitivity value not rated; torque transmission and costs HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11646,12 +11646,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_SPOOL_RETENTION</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 98 with keyed clutch collar seat</t>
+          <t>two split external rings in shaft grooves plus right loose-flange thrust washer</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11661,22 +11661,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel ring + washer candidate</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>AXIAL_PATH_GEOMETRY_ONLY</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Shaft bearing and key torque rating HOLD; UNQUOTED</t>
+          <t>Rings y96..97 and y168..169; washer y167..168; collar/spring/flanges contact nominally with no rated preload. Ring size/tolerance/fatigue/axial capacity and quote HOLD; unquoted NOT zero</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11703,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_SPOOL_SHAFT</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>filament path-buffer post + wrap arm</t>
+          <t>spool shaft dia 16 x 98 with keyed clutch collar seat and two 1 mm candidate external-ring grooves</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>C45 candidate</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>TENSION_UNRATED</t>
+          <t>WINDER_UNRATED</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Not a calibrated torque limiter; UNQUOTED</t>
+          <t>Groove root radius 7.2 mm at y96..97 and y168..169; fatigue and ring groove standard HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11760,12 +11760,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_TENSIONER</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>filament path-buffer post + wrap arm</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11775,12 +11775,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>TENSION_UNRATED</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Not a calibrated torque limiter; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11817,50 +11817,107 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G209" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H209" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
+      <c r="I209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K209" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -11252,7 +11252,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>keyed collar + spring envelope + friction washer between driven shaft and loose spool flange</t>
+          <t>keyed collar + unselected 1 mm spring envelope + friction washer between driven shaft and loose spool flange</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>steel collar + friction pad + spring reference</t>
+          <t>steel collar + friction pad + spring unselected</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Separate groove-backed retention closes candidate axial path; actual spring compression/preload and 70 Nmm sensitivity value not rated; torque transmission and costs HOLD; UNQUOTED</t>
+          <t>Smalley SSB-0087 clears dia16 shaft but its published 1.57 mm work height exceeds current 1 mm seat by 0.57 mm; solid height/force there unknown. Cannot assign the 62.3 N vendor work-point load or 70 Nmm model torque to assembly; no selected spring or quote</t>
         </is>
       </c>
     </row>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>two split external rings in shaft grooves plus right loose-flange thrust washer</t>
+          <t>two ES-16 nominal external-ring envelopes plus loose-flange OD30/ID16.2 thrust washer</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11661,12 +11661,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>steel ring + washer candidate</t>
+          <t>ring spring steel candidate + steel washer</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AXIAL_PATH_GEOMETRY_ONLY</t>
+          <t>AXIAL_FLOAT_PRELOAD_HOLD</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Rings y96..97 and y168..169; washer y167..168; collar/spring/flanges contact nominally with no rated preload. Ring size/tolerance/fatigue/axial capacity and quote HOLD; unquoted NOT zero</t>
+          <t>Smalley ES-16 two-turn supplier detail unmodeled; 15.02 mm groove dia and 1.00 +0.08 mm width; nominal 0.89 +/-0.05 mm ring thickness and 1.40 +0.08/-0.13 radial wall. Groove clearance 0.06..0.24 mm per ring (two up to 0.48 mm) excludes rated clamp; maker groove yield 3820 N assumes 45000 psi shaft yield/SF2 and is NOT a PPR rating. MPN dimension reference only; installed fit/thrust/fatigue/landed price HOLD; unquoted NOT zero</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11708,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 98 with keyed clutch collar seat and two 1 mm candidate external-ring grooves</t>
+          <t>spool shaft dia 16 x 98 with keyed clutch collar seat and two ES-16 dimensional-candidate 1 mm grooves</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Groove root radius 7.2 mm at y96..97 and y168..169; fatigue and ring groove standard HOLD; UNQUOTED</t>
+          <t>Groove nominal diameter 15.02 mm at y96..97 and y168..169; supplier Dg tolerance +/-0.075 mm; shaft fatigue/actual ring procurement HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -9998,7 +9998,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>puller base and side plates with bored Ø8.4 axle seats and east bearing web</t>
+          <t>puller base and two Ø8.4 drive seats with slotted idler-axle plates, vertical Ø5 guides and spring caps</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + 3 mm</t>
+          <t>steel plate + guide rod candidates</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>Ø20 rollers center the filament 11 mm inboard of both roller ends; bearing selection and carriage linear guide still HOLD; UNQUOTED</t>
+          <t>1.5 mm idler translation has geometric clearance; bearing inserts and side-plate/cap/guide joints not selected; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PULL_MOTOR_REF</t>
+          <t>PULL_IDLER_CARRIAGE</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>puller gearmotor reference (not selected)</t>
+          <t>two translating axle bearing seats joined behind roller</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -10065,22 +10065,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate candidate</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>0..1.5 mm vertical stroke on two Ø5 guides with Ø5.2 sliding bores; tolerances/racking and fatigue unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10107,22 +10107,22 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PULL_NIP_STOP</t>
+          <t>PULL_IDLER_SPRINGS</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>underside seat at 1.5 mm roller nip; touches frame/carriage without penetration</t>
+          <t>two vertical compression spring space envelopes</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>springs unselected</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>Stop attachment and open setting hardware unqualified; UNQUOTED</t>
+          <t>Installed height 8.5..7.0 mm over stroke; no free height/solid height/rate/preload or working traction assigned; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_ADJ</t>
+          <t>PULL_MOTOR_REF</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>puller adjustable roller dia 20 + spring-loaded carriage and guide-post envelopes</t>
+          <t>puller gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>steel + springs unselected</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>NIP_RATING_HOLD</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>At modeled minimum gap 1.5 mm the 1.75 mm strand intersects both compliant roller envelopes; actual spring force and guide travel not rated; UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PULL_ROLLER_FIXED</t>
+          <t>PULL_NIP_STOP</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>puller drive roller dia 20 x 22</t>
+          <t>two lower and two upper positive seats limiting gap 1.5..3.0 mm</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>steel; knurl or rubber per TPU grip</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Stops contact carrier only at end positions; attachment and shock loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10278,37 +10278,37 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>S1_BELT</t>
+          <t>PULL_ROLLER_ADJ</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
+          <t>independently rotating idler dia 20 x 22 with Ø6 axle</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>polymer belt with steel-supported drums</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Friction and tension unrated; UNQUOTED</t>
+          <t>Idler axle clears carrier nominal Ø6.04 bearing-envelope bore; bushing and axle retention unselected; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10335,12 +10335,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>S1_BELT_BEARINGS</t>
+          <t>PULL_ROLLER_FIXED</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>four belt shaft support rings in the side rails</t>
+          <t>puller driven roller dia 20 x 22 with Ø8 axle</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel; knurl or rubber per TPU grip</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>TRANSFER_UNRATED</t>
+          <t>NIP_RATING_HOLD</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>Bearing selection and loads unqualified; UNQUOTED</t>
+          <t>Drive bearings and grip unselected; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10392,22 +10392,22 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>S1_BELT_CHAIN</t>
+          <t>S1_BELT</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>#35 chain from S1B 24T to west belt 12T</t>
+          <t>two side-loop treads over x80..219; y163.5..223.2 and 240.8..323.5</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ANSI35 steel chain</t>
+          <t>polymer belt with steel-supported drums</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>Tension and strength unrated; UNQUOTED</t>
+          <t>Friction and tension unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10449,12 +10449,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S1_BELT_DRIVE</t>
+          <t>S1_BELT_BEARINGS</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
+          <t>four belt shaft support rings in the side rails</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>steel shaft and drums</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10494,7 +10494,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
+          <t>Bearing selection and loads unqualified; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S1_BELT_FOLLOWER</t>
+          <t>S1_BELT_CHAIN</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>12T sprocket on the west belt driver</t>
+          <t>#35 chain from S1B 24T to west belt 12T</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>ANSI35 steel sprocket</t>
+          <t>ANSI35 steel chain</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Tension and strength unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10563,12 +10563,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>S1_BELT_IDLER</t>
+          <t>S1_BELT_DRIVE</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
+          <t>common waisted drive drum at x80; separate r3.8 side and r2.3 central tread seats</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>steel journals and drums</t>
+          <t>steel shaft and drums</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Two independent journal halves; UNQUOTED</t>
+          <t>S1B chain-driven; torque and bearing load unrated; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10620,12 +10620,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>S1_SWEEP_BEARINGS</t>
+          <t>S1_BELT_FOLLOWER</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>two separated sweep bearing rings in the pan rails</t>
+          <t>12T sprocket on the west belt driver</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>ANSI35 steel sprocket</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_N</t>
+          <t>S1_BELT_IDLER</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>12T gear on the north east belt idler</t>
+          <t>two split side idler drums at x219 leaving the central transfer corridor open</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel journals and drums</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Two independent journal halves; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10734,12 +10734,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_DRUM_S</t>
+          <t>S1_SWEEP_BEARINGS</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>12T gear on the south east belt idler</t>
+          <t>two separated sweep bearing rings in the pan rails</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>steel gear</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_N</t>
+          <t>S1_SWEEP_GEAR_DRUM_N</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>12T gear on the north sweep shaft</t>
+          <t>12T gear on the north east belt idler</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>S1_SWEEP_GEAR_S</t>
+          <t>S1_SWEEP_GEAR_DRUM_S</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>12T gear on the south sweep shaft</t>
+          <t>12T gear on the south east belt idler</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>S1_SWEEP_NORTH</t>
+          <t>S1_SWEEP_GEAR_N</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>north transverse screw x224 y235.5..359 radius 7.2 flight feeding central lane</t>
+          <t>12T gear on the north sweep shaft</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Swept flight reaches previously stranded Ø3 mm envelope near x223/z336.5; actual same-particle pickup untested; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>S1_SWEEP_SOUTH</t>
+          <t>S1_SWEEP_GEAR_S</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>south transverse screw x224 y127..228.5 radius 7.2 flight feeding central lane</t>
+          <t>12T gear on the south sweep shaft</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>steel shaft and flight</t>
+          <t>steel gear</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Floor relief provides swept clearance; flake capture and torque not proven; UNQUOTED</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11019,12 +11019,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BEARINGS</t>
+          <t>S1_SWEEP_NORTH</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>two central idler support rings</t>
+          <t>north transverse screw x224 y235.5..359 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>steel bearing seats</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>VP1-STAGE5</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Swept flight reaches previously stranded Ø3 mm envelope near x223/z336.5; actual same-particle pickup untested; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11076,12 +11076,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_BELT</t>
+          <t>S1_SWEEP_SOUTH</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>central 17 mm tread from x80 to x270 inside two side loops</t>
+          <t>south transverse screw x224 y127..228.5 radius 7.2 flight feeding central lane</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>polymer belt</t>
+          <t>steel shaft and flight</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Extended drum and ramp towards auger inlet; traction and throughflow unproven; UNQUOTED</t>
+          <t>Floor relief provides swept clearance; flake capture and torque not proven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11133,12 +11133,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>S1_TRANSFER_IDLER</t>
+          <t>S1_TRANSFER_BEARINGS</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>central east r2.05/2.45 idler at x270</t>
+          <t>two central idler support rings</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>steel drum</t>
+          <t>steel bearing seats</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SERVICE-HOPPER</t>
+          <t>S1_TRANSFER_BELT</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>SWAP hollow side-inlet for reference material on FEED-BUF saddle; not in production assembly</t>
+          <t>central 17 mm tread from x80 to x270 inside two side loops</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -11205,22 +11205,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>steel sheet 3 mm</t>
+          <t>polymer belt</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>SWAP_PART_NO_INTERLOCK</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>VP1-STAGE6</t>
+          <t>VP1-STAGE5</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>VP1-STAGE6</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>S2 off; saddle seal/fasteners and flow remain HOLD; no interlock credit; UNQUOTED</t>
+          <t>Extended drum and ramp towards auger inlet; traction and throughflow unproven; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11247,12 +11247,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>WIND_CLUTCH_REF</t>
+          <t>S1_TRANSFER_IDLER</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>keyed collar + unselected 1 mm spring envelope + friction washer between driven shaft and loose spool flange</t>
+          <t>central east r2.05/2.45 idler at x270</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -11262,24 +11262,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>steel collar + friction pad + spring unselected</t>
+          <t>steel drum</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>TORQUE_LIMIT_UNQUALIFIED</t>
+          <t>TRANSFER_UNRATED</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
+          <t>VP1-STAGE5</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
           <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>VP1-REFERENCE-FEED</t>
-        </is>
-      </c>
       <c r="I198" t="inlineStr">
         <is>
           <t/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Smalley SSB-0087 clears dia16 shaft but its published 1.57 mm work height exceeds current 1 mm seat by 0.57 mm; solid height/force there unknown. Cannot assign the 62.3 N vendor work-point load or 70 Nmm model torque to assembly; no selected spring or quote</t>
+          <t>UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11304,12 +11304,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_L</t>
+          <t>SERVICE-HOPPER</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>SWAP hollow side-inlet for reference material on FEED-BUF saddle; not in production assembly</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11319,22 +11319,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel sheet 3 mm</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>SWAP_PART_NO_INTERLOCK</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-STAGE6</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>S2 off; saddle seal/fasteners and flow remain HOLD; no interlock credit; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WIND_FLANGE_R</t>
+          <t>WIND_CLUTCH_REF</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>spool flange dia 200 x 3 mm</t>
+          <t>keyed collar + unselected 1 mm spring envelope + friction washer between driven shaft and loose spool flange</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -11376,22 +11376,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>steel plate 3 mm screening candidate</t>
+          <t>steel collar + friction pad + spring unselected</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
+          <t>TORQUE_LIMIT_UNQUALIFIED</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
+          <t>Smalley SSB-0087 clears dia16 shaft but its published 1.57 mm work height exceeds current 1 mm seat by 0.57 mm; solid height/force there unknown. Cannot assign the 62.3 N vendor work-point load or 70 Nmm model torque to assembly; no selected spring or quote</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>WIND_MOTOR_REF</t>
+          <t>WIND_FLANGE_L</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>spool gearmotor reference (not selected)</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>24 V gearmotor MPN unselected</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>MOTOR_UNSELECTED</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -11475,12 +11475,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>WIND_MOUNT</t>
+          <t>WIND_FLANGE_R</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>steel cantilever with front-profile face plate, two bearing rails and motor bed</t>
+          <t>spool flange dia 200 x 3 mm</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -11490,22 +11490,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>steel plate/bar 4-8 mm + M5 candidate clearances</t>
+          <t>steel plate 3 mm screening candidate</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>WINDER_JOINT_HOLD</t>
+          <t>WINDER_STIFFNESS_SCREEN_PASS_HUB_HOLD</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>BRep face contact to FR-2020-400_001 and bearing/motor seats; profile slot, fastener/weld sizes, cantilever stiffness, vibration and guard HOLD; no quote - NOT 0</t>
+          <t>20 N assumed rim load; 43.33 MPa/0.194 mm beam screen only; hub bolt balance guard unqualified; unquoted</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_BEARINGS</t>
+          <t>WIND_MOTOR_REF</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>spool shaft bearing blocks at BOTH shaft ends</t>
+          <t>spool gearmotor reference (not selected)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -11547,22 +11547,22 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>steel plate 5 mm + bearing seats</t>
+          <t>24 V gearmotor MPN unselected</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>MOTOR_UNSELECTED</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE2</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>VP1-STAGE4</t>
+          <t>VP1-STAGE3</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
+          <t>UNQUOTED; known motor floors exceed the 100000 KRW soft limit - not 0</t>
         </is>
       </c>
     </row>
@@ -11589,12 +11589,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_DRUM</t>
+          <t>WIND_MOUNT</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>spool dia 70 x 58 steel tube with 2 mm wall and two 3 mm internal annular webs; weld to steel flanges before winding</t>
+          <t>steel cantilever with front-profile face plate, two bearing rails and motor bed</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>steel tube + steel webs candidate</t>
+          <t>steel plate/bar 4-8 mm + M5 candidate clearances</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>WINDER_UNRATED</t>
+          <t>WINDER_JOINT_HOLD</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Web-to-tube and flange seams and balance unqualified; loose Ø17 web bores clear Ø16 shaft; friction clutch drives flange; UNQUOTED</t>
+          <t>BRep face contact to FR-2020-400_001 and bearing/motor seats; profile slot, fastener/weld sizes, cantilever stiffness, vibration and guard HOLD; no quote - NOT 0</t>
         </is>
       </c>
     </row>
@@ -11646,12 +11646,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_RETENTION</t>
+          <t>WIND_SPOOL_BEARINGS</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>two ES-16 nominal external-ring envelopes plus loose-flange OD30/ID16.2 thrust washer</t>
+          <t>spool shaft bearing blocks at BOTH shaft ends</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -11661,22 +11661,22 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>ring spring steel candidate + steel washer</t>
+          <t>steel plate 5 mm + bearing seats</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>AXIAL_FLOAT_PRELOAD_HOLD</t>
+          <t>WINDER_UNRATED</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>VP1-REFERENCE-FEED</t>
+          <t>VP1-STAGE4</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Smalley ES-16 two-turn supplier detail unmodeled; 15.02 mm groove dia and 1.00 +0.08 mm width; nominal 0.89 +/-0.05 mm ring thickness and 1.40 +0.08/-0.13 radial wall. Groove clearance 0.06..0.24 mm per ring (two up to 0.48 mm) excludes rated clamp; maker groove yield 3820 N assumes 45000 psi shaft yield/SF2 and is NOT a PPR rating. MPN dimension reference only; installed fit/thrust/fatigue/landed price HOLD; unquoted NOT zero</t>
+          <t>VP1 Stage 4 grip redesign: shaft supported at both ends - UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11703,12 +11703,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>WIND_SPOOL_SHAFT</t>
+          <t>WIND_SPOOL_DRUM</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>spool shaft dia 16 x 98 with keyed clutch collar seat and two ES-16 dimensional-candidate 1 mm grooves</t>
+          <t>spool dia 70 x 58 steel tube with 2 mm wall and two 3 mm internal annular webs; weld to steel flanges before winding</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>C45 candidate</t>
+          <t>steel tube + steel webs candidate</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Groove nominal diameter 15.02 mm at y96..97 and y168..169; supplier Dg tolerance +/-0.075 mm; shaft fatigue/actual ring procurement HOLD; UNQUOTED</t>
+          <t>Web-to-tube and flange seams and balance unqualified; loose Ø17 web bores clear Ø16 shaft; friction clutch drives flange; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11760,12 +11760,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>WIND_TENSIONER</t>
+          <t>WIND_SPOOL_RETENTION</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>filament path-buffer post + wrap arm</t>
+          <t>two ES-16 nominal external-ring envelopes plus loose-flange OD30/ID16.2 thrust washer</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -11775,22 +11775,22 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>ring spring steel candidate + steel washer</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>TENSION_UNRATED</t>
+          <t>AXIAL_FLOAT_PRELOAD_HOLD</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Not a calibrated torque limiter; UNQUOTED</t>
+          <t>Smalley ES-16 two-turn supplier detail unmodeled; 15.02 mm groove dia and 1.00 +0.08 mm width; nominal 0.89 +/-0.05 mm ring thickness and 1.40 +0.08/-0.13 radial wall. Groove clearance 0.06..0.24 mm per ring (two up to 0.48 mm) excludes rated clamp; maker groove yield 3820 N assumes 45000 psi shaft yield/SF2 and is NOT a PPR rating. MPN dimension reference only; installed fit/thrust/fatigue/landed price HOLD; unquoted NOT zero</t>
         </is>
       </c>
     </row>
@@ -11817,12 +11817,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>WIND_TRAVERSE_RIDER</t>
+          <t>WIND_SPOOL_SHAFT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>traverse rider block + guide eyelet</t>
+          <t>spool shaft dia 16 x 98 with keyed clutch collar seat and two ES-16 dimensional-candidate 1 mm grooves</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>steel + printed guide</t>
+          <t>C45 candidate</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>VP1-STAGE2</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>VP1-STAGE3</t>
+          <t>VP1-REFERENCE-FEED</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>UNQUOTED</t>
+          <t>Groove nominal diameter 15.02 mm at y96..97 and y168..169; supplier Dg tolerance +/-0.075 mm; shaft fatigue/actual ring procurement HOLD; UNQUOTED</t>
         </is>
       </c>
     </row>
@@ -11874,50 +11874,164 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
+          <t>WIND_TENSIONER</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>filament path-buffer post + wrap arm</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>TENSION_UNRATED</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Not a calibrated torque limiter; UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>WIND_TRAVERSE_RIDER</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>traverse rider block + guide eyelet</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>steel + printed guide</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>WINDER_UNRATED</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>VP1-STAGE2</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>VP1-STAGE3</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>UNQUOTED_NOT_ZERO</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>UNQUOTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>vp1_stage1_3</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
           <t>WIND_TRAVERSE_SCREW</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>traverse lead screw dia 8 x 80</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
         <is>
           <t>steel rod</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>WINDER_UNRATED</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>VP1-STAGE2</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>VP1-STAGE3</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
+      <c r="I211" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
         <is>
           <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K211" t="inlineStr">
         <is>
           <t>UNQUOTED</t>
         </is>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Owned 24V 800W PSU</t>
+          <t>24V 800W PSU</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>OWNED_MOUNTING_PATTERN_UNMEASURED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>No guessed mounting holes. 120x240x65 user measurement; model contains true body only.</t>
+          <t>No guessed mounting holes. 120x240x65 historical reference envelope; model contains true body only. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5562,12 +5562,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5577,22 +5577,22 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5634,22 +5634,22 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5676,12 +5676,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5691,22 +5691,22 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5748,22 +5748,22 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5790,12 +5790,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5805,22 +5805,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5862,22 +5862,22 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Al extrusion - existing</t>
+          <t>Al extrusion candidate</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>OWNED_SLOT_PATTERN_TO_MEASURE</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5919,22 +5919,22 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OWNED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6717,22 +6717,22 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware.</t>
+          <t>Reference power allocator is NOT deployable heater firmware. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Existing BTS7960 modules</t>
+          <t>BTS7960 modules</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OWNED_UNQUALIFIED</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6831,22 +6831,22 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous.</t>
+          <t>Do not assume advertised43A continuous. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Existing E-stop</t>
+          <t>E-stop</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>OWNED_RATING_VERIFY</t>
+          <t>PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7401,22 +7401,22 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>C1_INTERFACE_BASELINE</t>
+          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>OWNED_NO_NEW_PURCHASE</t>
+          <t>UNQUOTED_NOT_ZERO</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify.</t>
+          <t>Independent hard cut with contactor; contact configuration verify. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
         </is>
       </c>
     </row>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>24V 800W PSU</t>
+          <t>User-reported Anycubic Chiron donor PSU, 24V 800W (label unverified)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Donor PSU (unverified)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>OWNED_REPORTED_RATING_HOLD</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>USER_REPORTED_CHIRON_PSU_LABEL_UNVERIFIED</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>UNQUOTED_NOT_ZERO</t>
+          <t>OWNED_DONOR_PSU_NO_NEW_PURCHASE_UNQUALIFIED</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>No guessed mounting holes. 120x240x65 historical reference envelope; model contains true body only. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>No guessed mounting holes. 120x240x65 historical modeled envelope; model contains true body only. Chiron donor PSU reported owned; 24V 800W is historical user report and 240x120x65 mm is a modeled envelope, not a measured nameplate or fit. Check label, dimensions, condition, protection and 500W staged duty; no replacement PSU purchase assumed.</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>DONOR_CUT_FIT_OR_PROCUREMENT_HOLD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Nominal section only. Confirm slot series before buying brackets; 3 mm saw kerf. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Reference power allocator is NOT deployable heater firmware. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Reference power allocator is NOT deployable heater firmware. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>C1_GEOMETRY_REFERENCE_CURRENT_STOCK_UNCONFIRMED</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Do not assume advertised43A continuous. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Do not assume advertised43A continuous. Historical handover is not current qualified stock; confirm donor part identity/interface or obtain landed quote.</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Configurable current limit; board21A is not terminal43A. Existing BTS7960 requires qualification.</t>
+          <t>Configurable current limit; board21A is not terminal43A. BTS7960 candidate requires qualification.</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>E-stop</t>
+          <t>User-reported 2NC emergency stop button</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PROCUREMENT_HOLD</t>
+          <t>OWNED_REPORTED_RATING_HOLD</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>C1_GEOMETRY_REFERENCE_USER_REPORTS_NO_STOCK</t>
+          <t>USER_REPORTED_2NC_BUTTON_MODEL_UNVERIFIED</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>UNQUOTED_NOT_ZERO</t>
+          <t>OWNED_BUTTON_NO_NEW_PURCHASE_UNQUALIFIED</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify. Historical handover assumed stock; current user reports none. Obtain landed quote; not zero.</t>
+          <t>Independent hard cut with contactor; contact configuration verify. One 2NC button reported owned; model, contact rating, positive opening, wiring and hard-cut contactor unverified. No additional button purchase assumed; full safety circuit still unquoted.</t>
         </is>
       </c>
     </row>

--- a/c2.1/bom/system_bom.xlsx
+++ b/c2.1/bom/system_bom.xlsx
@@ -4680,7 +4680,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>No guessed mounting holes. 120x240x65 historical modeled envelope; model contains true body only. Chiron donor PSU reported owned; 24V 800W is historical user report and 240x120x65 mm is a modeled envelope, not a measured nameplate or fit. Check label, dimensions, condition, protection and 500W staged duty; no replacement PSU purchase assumed.</t>
+          <t>No guessed mounting holes. 240x120x65 mm user-reported exterior; CAD box is an exterior envelope only. Chiron donor PSU reported owned; 24V 800W is user-reported. Label, mounting pattern, condition, protection and 500W staged duty remain unverified; no replacement PSU purchase assumed.</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Independent hard cut with contactor; contact configuration verify. One 2NC button reported owned; model, contact rating, positive opening, wiring and hard-cut contactor unverified. No additional button purchase assumed; full safety circuit still unquoted.</t>
+          <t>Independent hard cut with contactor; contact configuration verify. One 2NC button reported owned, with a reported 35x35 mm size (which face, body depth and panel cutout unidentified); model, contact rating, positive opening, wiring and hard-cut contactor unverified. No additional button purchase assumed; full safety circuit unquoted.</t>
         </is>
       </c>
     </row>
